--- a/cruce_hojas_tanda1.xlsx
+++ b/cruce_hojas_tanda1.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conceptos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce'!$A$1:$X$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce'!$A$1:$U$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conceptos'!$A$1:$H$740</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X137"/>
+  <dimension ref="A1:U137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -479,18 +479,15 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="45" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="35" customWidth="1" min="19" max="19"/>
-    <col width="50" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,60 +553,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Hoja de Monday que completa</t>
+          <t>Firmada (fichero)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Monday: candidatas</t>
+          <t>Enviada (documento)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Firmada (fichero)</t>
+          <t>Enviada: carpeta</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Enviada (documento)</t>
+          <t>Enviada: última modificación</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Enviada: carpeta</t>
+          <t>Otras versiones en la carpeta</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Enviada: última modificación</t>
+          <t>Notas de la lectura</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Otras versiones en la carpeta</t>
+          <t>Código HE</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Notas de la lectura</t>
+          <t>Opp</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Código que ya trae la hoja</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Código HE</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Opp</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TU DECISIÓN</t>
         </is>
@@ -666,42 +648,33 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>subv ACCESIB · SUBVENCION · devuelta_firmada · 2000-01-01 · id 54194f79</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
+          <t>valdesangil 14 a 24 madrid subvenciones a exito pry externo 28-10-2024.pdf</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>HOJA ENCARGO VALDESANGIL 14 AL 24 MADRID SUBVENCION .docx</t>
+        </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>valdesangil 14 a 24 madrid subvenciones a exito pry externo 28-10-2024.pdf</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>HOJA ENCARGO VALDESANGIL 14 AL 24 MADRID SUBVENCION .docx</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>varios portales en una hoja (14 al 24); solo a éxito 2,5%</t>
         </is>
       </c>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -756,38 +729,29 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>PERICIAL · PERICIAL · devuelta_firmada · 2000-01-01 · id 493a7b3d</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>1</v>
+          <t>FERNANDEZ DE LOS RIOS 38 MADRID INFORME ESTRUCTURAL 05-11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>HOJA ENCARGO FERNANDEZ DE LOS RIOS 38 MADRID.docx</t>
+        </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>FERNANDEZ DE LOS RIOS 38 MADRID INFORME ESTRUCTURAL 05-11-2024.pdf</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>HOJA ENCARGO FERNANDEZ DE LOS RIOS 38 MADRID.docx</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -795,16 +759,12 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2024-11-15</t>
@@ -845,36 +805,31 @@
           <t>100% del importe en el momento del encargo mediante transferencia</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>av dos de mayo 73 mostoles subvenciones 15-11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>HOJA ENCARGO av dos de mayo 73 mostoles SUBVENCION fijo pry propio transferencia (1).pdf</t>
+        </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>av dos de mayo 73 mostoles subvenciones 15-11-2024.pdf</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>HOJA ENCARGO av dos de mayo 73 mostoles SUBVENCION fijo pry propio transferencia (1).pdf</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -937,42 +892,33 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>subv SATE EXTERNO · SUBVENCION · devuelta_firmada · 2000-01-01 · id a9d2df29</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>1</v>
+          <t>VILLALON 1 FUENLABRADA - SUBVENCIONES PRY EXTERNO 20-11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO villalon 1 fuenlabrada SUBVENCIONES SATE Y NG fijo + EXITO.docx</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>VILLALON 1 FUENLABRADA - SUBVENCIONES PRY EXTERNO 20-11-2024.pdf</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO villalon 1 fuenlabrada SUBVENCIONES SATE Y NG fijo + EXITO.docx</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>total = 1.500 fijo + 3% a éxito; la cabecera dice 'Proyecto para Rehabilitación de Envolvente Térmica' pero solo se cobra la tramitación de subvenciones; 'Otra Documentación Técnica' sin bloque</t>
         </is>
       </c>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1033,42 +979,33 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS, IEE · devuelta_firmada · 2000-01-01 · id fddbb349</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>1</v>
+          <t>solsona 7 madrid pry df css e iee 21-11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO solsona 7 madrid ASCENSOR + CSS + IEE UREKA .docx</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>solsona 7 madrid pry df css e iee 21-11-2024.pdf</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO solsona 7 madrid ASCENSOR + CSS + IEE UREKA .docx</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 5.900 sin desglose por concepto</t>
         </is>
       </c>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1083,7 +1020,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>la firmada se llama "no vale/anulado"; 0 hojas de Monday en esa dirección</t>
+          <t>la firmada se llama "no vale/anulado"</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1099,40 +1036,35 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>no vale ESCUELAS PIAS 1 ALCALA DF Y CSS PRY EXTERNO 27-11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>no vale ESCUELAS PIAS 1 ALCALA DF Y CSS PRY EXTERNO 27-11-2024.pdf</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>no vale ESCUELAS PIAS 1 ALCALA DF Y CSS PRY EXTERNO 27-11-2024.pdf</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>no vale ESCUELAS PIAS 1 ALCALA DF Y CSS PRY EXTERNO 27-11-2024.pdf</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS MODELOS</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>sin texto</t>
         </is>
       </c>
-      <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1189,42 +1121,33 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 0f76961d</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>1</v>
+          <t>JOSUE LILLO 5 MADRID 17-12-2024 (2).pdf</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO JOSUE LILLO 5 MADRID PRY ASC.docx</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>JOSUE LILLO 5 MADRID 17-12-2024 (2).pdf</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO JOSUE LILLO 5 MADRID PRY ASC.docx</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>la línea de 3.760 agrupa toma de datos, modelado 3D, proyecto y dirección de obra; casada a REDACCION PROYECTO</t>
         </is>
       </c>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1285,42 +1208,33 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>subv SATE EXTERNO · SUBVENCION, LIBRO, CAES · devuelta_firmada · 2000-01-01 · id f88c3bf1</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>1</v>
+          <t>ALTAMIRANO 48 MADRID SUBVENCIONES 03-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO ALTAMIRANO 48 MADRID SUBV ENERGETICA.docx</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ALTAMIRANO 48 MADRID SUBVENCIONES 03-01-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO ALTAMIRANO 48 MADRID SUBV ENERGETICA.docx</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>solo a éxito 2,5%, sin importe fijo; incluye monetización por CAEs; 'Otra Documentación Técnica' sin bloque</t>
         </is>
       </c>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1379,42 +1293,33 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>PERICIAL · PERICIAL · devuelta_firmada · 2000-01-01 · id 710eb2dc</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
+          <t>GINZO DE LIMIA 55 MADRID calculo estructural 03-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>HOJA ENCARGO GINZO DE LIMIA 55 MADRID.docx</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>GINZO DE LIMIA 55 MADRID calculo estructural 03-01-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>HOJA ENCARGO GINZO DE LIMIA 55 MADRID.docx</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 009 (duplicado); pagador sin nombre, la casilla Nº pedido sugiere contrata</t>
         </is>
       </c>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1473,42 +1378,33 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>PERICIAL · PERICIAL · devuelta_firmada · 2000-01-01 · id 710eb2dc</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>1</v>
+          <t>GINZO DE LIMIA 55 MADRID INSTRUCCIONES FAIN FACTURAS A 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>HOJA ENCARGO GINZO DE LIMIA 55 MADRID.docx</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>GINZO DE LIMIA 55 MADRID INSTRUCCIONES FAIN FACTURAS A 04-01-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>HOJA ENCARGO GINZO DE LIMIA 55 MADRID.docx</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 008 (duplicado); pagador sin nombre, la casilla Nº pedido sugiere contrata</t>
         </is>
       </c>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1523,7 +1419,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>más de 6 meses entre hoja y firma; 0 hojas de Monday en esa dirección</t>
+          <t>más de 6 meses entre hoja y firma</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1568,40 +1464,35 @@
           <t>50% al encargo, 50% a la entrega de proyecto</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>CASTILLA LA NUEVA 33 FUENLABRADA 13-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO castilla la nueva 33 fuenlabrada ACCESIBILIDAD PRY+DF.docx</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CASTILLA LA NUEVA 33 FUENLABRADA 13-01-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO castilla la nueva 33 fuenlabrada ACCESIBILIDAD PRY+DF.docx</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>proyecto + licencia + DF a precio conjunto de 2.500; accesibilidad en planta baja</t>
         </is>
       </c>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1664,42 +1555,33 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>subv CUBIERTA · SUBVENCION, IEE, LIBRO · devuelta_firmada · 2000-01-01 · id f0acc7b9</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>1</v>
+          <t>PEIRONCELY 40 MADRID SUBV CUBIERTA 30-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>PEIRONCELY 40 MADRID HOJA DE ENCARGO SUBVENCIONES 22-01-2025.docx</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>PEIRONCELY 40 MADRID SUBV CUBIERTA 30-01-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>PEIRONCELY 40 MADRID HOJA DE ENCARGO SUBVENCIONES 22-01-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 1.980 para todo; subvenciones de accesibilidad y eficiencia juntas, casado al bloque genérico; sin cabecera de empresa</t>
         </is>
       </c>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1758,42 +1640,33 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION, DIR. OBRA · devuelta_firmada · 2000-01-01 · id a281b1da</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1</v>
+          <t>SANTA EDUVIGIS 5 MADRID ASC 05-02-2025.gdoc</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>SANTA EDUVIGIS 5 MADRID ASCENSOR + SUBV 31-01-2025.docx</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>SANTA EDUVIGIS 5 MADRID ASC 05-02-2025.gdoc</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>SANTA EDUVIGIS 5 MADRID ASCENSOR + SUBV 31-01-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 013 (duplicado); proyecto+licencia+DF+CFO a precio conjunto de 5.500; total 7.480 calculado (la hoja no da total)</t>
         </is>
       </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1852,42 +1725,33 @@
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION, DIR. OBRA · devuelta_firmada · 2000-01-01 · id a281b1da</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>1</v>
+          <t>SANTA EDUVIGIS 5 MADRID ASC 05-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>SANTA EDUVIGIS 5 MADRID ASCENSOR + SUBV 31-01-2025.docx</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>SANTA EDUVIGIS 5 MADRID ASC 05-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>SANTA EDUVIGIS 5 MADRID ASCENSOR + SUBV 31-01-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 012 (duplicado); proyecto+licencia+DF+CFO a precio conjunto de 5.500; total 7.480 calculado (la hoja no da total)</t>
         </is>
       </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1895,16 +1759,12 @@
           <t>014</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2025-02-17</t>
@@ -1947,40 +1807,35 @@
           <t>50% a la entrega de proyecto, 30% a la obtención de licencia, 20% al fin de obra</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="n">
-        <v>0</v>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>HUMERA 16 FUENLABRADA FAIN BAJADA A COTA CERO 17-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>HUMERA 16 FUENLABRADA COTA CERO FAIN PRY.docx</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>HUMERA 16 FUENLABRADA FAIN BAJADA A COTA CERO 17-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>HUMERA 16 FUENLABRADA COTA CERO FAIN PRY.docx</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 2.500 sin desglose</t>
         </is>
       </c>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2039,42 +1894,33 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id 09d33fc9</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1</v>
+          <t>av marques de corbera 30b madrid pry y subv 18-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO av marques de corbera 30b madrid pry css df subvenciones.docx</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>av marques de corbera 30b madrid pry y subv 18-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO av marques de corbera 30b madrid pry css df subvenciones.docx</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>dos precios conjuntos: 6.000 (proyecto+licencia+subvenciones) y 4.000 (DF+CSS); total 10.000 sumado</t>
         </is>
       </c>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2089,7 +1935,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0 hojas de Monday en esa dirección; la lectura avisa de algo raro</t>
+          <t>la lectura avisa de algo raro</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2135,40 +1981,35 @@
           <t>50% a la entrega de proyecto, 30% a la obtención de licencia, 20% al fin de obra</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>severo ochoa 10 fuenlabrada ascensor fain 18-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>SEVERO OCHOA 10 FUENLABRADA HOJA DE ENCARGO ASCENSOR 18-02-2025.docx</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>severo ochoa 10 fuenlabrada ascensor fain 18-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>SEVERO OCHOA 10 FUENLABRADA HOJA DE ENCARGO ASCENSOR 18-02-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 3.100; el texto cita la Ordenanza y el Ayuntamiento de Madrid aunque el edificio está en Fuenlabrada (texto posiblemente copiado de otra hoja)</t>
         </is>
       </c>
-      <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2235,42 +2076,33 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SATE · PROYECTO, DIR. OBRA, CSS, SUBVENCION, LIBRO · devuelta_firmada · 2000-01-01 · id 15bec43a</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>1</v>
+          <t>AVDA DE LA MANCHA 15 LEGANES SATE 20-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>AV MANCHA 15 LEGANES SATE 17-02-2025.docx</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>AVDA DE LA MANCHA 15 LEGANES SATE 20-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>AV MANCHA 15 LEGANES SATE 17-02-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>el fichero lleva antes otra propuesta sin fecha para C/ Virgen del Camino 17 Leganés (envolvente y cubierta, 9.763 € desglosados); solo la de AV MANCHA 15 tiene fecha y firma; resto de conceptos sin precio (11.000 conjunto); SATE fachada dudoso (dice envolvente)</t>
         </is>
       </c>
-      <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2285,7 +2117,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2 hojas de Monday en esa dirección; la lectura avisa de algo raro</t>
+          <t>la lectura avisa de algo raro</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2334,43 +2166,33 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id 9f38272a
-ASCENSOR · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id b09c1a63</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>2</v>
+          <t>ANGEL BARAJAS 4 POZUELO ASCENSOR pry css df subvenciones_firmada 24-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>ANGEL BARAJAS 4 POZUELO pry css df subvenciones.docx</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ANGEL BARAJAS 4 POZUELO ASCENSOR pry css df subvenciones_firmada 24-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>ANGEL BARAJAS 4 POZUELO pry css df subvenciones.docx</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 12.500; cita subvenciones del Ayuntamiento de Madrid aunque el edificio está en Pozuelo; pago ligado a consulta urbanística</t>
         </is>
       </c>
-      <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2426,42 +2248,33 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>SOLO DF · DIR. OBRA, CSS · devuelta_firmada · 2000-01-01 · id 10dedb85</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>1</v>
+          <t>ESCUELAS PIAS 1 ALCALA DF Y CSS 24-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO ESCUELAS PIAS 1 ALCALA solo DF y CSS.docx</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ESCUELAS PIAS 1 ALCALA DF Y CSS 24-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO ESCUELAS PIAS 1 ALCALA solo DF y CSS.docx</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>solo DF y CSS de una obra de ascensor; el proyecto no está en esta hoja</t>
         </is>
       </c>
-      <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2521,42 +2334,33 @@
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION · devuelta_firmada · 2000-01-01 · id e4e695c5</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>1</v>
+          <t>ILIADA 19 MADRID ASCENSOR Y SUBVENCIONES 27-02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO iliada 19 madrid ASCENSOR Y SUBV (2).docx</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ILIADA 19 MADRID ASCENSOR Y SUBVENCIONES 27-02-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO iliada 19 madrid ASCENSOR Y SUBV (2).docx</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>dos hojas en un fichero (proyecto 5.650 y subvenciones 1.980); total 7.630 sumado; la línea de 3.910 agrupa toma de datos, proyecto, visado y dirección de obra</t>
         </is>
       </c>
-      <c r="U22" s="2" t="n"/>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2612,42 +2416,33 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>SOLO DF · DIR. OBRA, CSS · devuelta_firmada · 2000-01-01 · id 21e30d9c</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>1</v>
+          <t>RIO TORMES 1 MOSTOLES HE DF+CSS 07-03-2025 (1).pdf</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>RIO TORMES 1 MOSTOLES HE DF+CSS 05-03-2025.docx</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>RIO TORMES 1 MOSTOLES HE DF+CSS 07-03-2025 (1).pdf</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>RIO TORMES 1 MOSTOLES HE DF+CSS 05-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 2.400 DF+CSS; obra de ascensor con proyecto externo; en la casilla CIF pone la razón social</t>
         </is>
       </c>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr"/>
-      <c r="X23" s="4" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2713,42 +2508,33 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>ACCESIB · PROYECTO, DIR. OBRA · devuelta_firmada · 2000-01-01 · id bf5af970</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1</v>
+          <t>SALVADOR DALI 6 PINTO RAMPA Y REMODELACION PORTAL 07-03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO SALVADOR DALI 6 PINTO.docx</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>SALVADOR DALI 6 PINTO RAMPA Y REMODELACION PORTAL 07-03-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO SALVADOR DALI 6 PINTO.docx</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 2.500; incluye remodelación de portal</t>
         </is>
       </c>
-      <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="4" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2756,16 +2542,12 @@
           <t>023</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2025-03-12</t>
@@ -2801,36 +2583,31 @@
         <v>300</v>
       </c>
       <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="n">
-        <v>0</v>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>AV PROVINCIAS 46 FUENLABRADA TRAMITACION DR 12-03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>AVENIDA DE LAS PROVINCIAS 46 FUENLABRADA TRAMITACION DR 11-03-2025.docx</t>
+        </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>AV PROVINCIAS 46 FUENLABRADA TRAMITACION DR 12-03-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>AVENIDA DE LAS PROVINCIAS 46 FUENLABRADA TRAMITACION DR 11-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr"/>
-      <c r="X25" s="4" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2887,42 +2664,33 @@
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA · devuelta_firmada · 2000-01-01 · id a3692cb2</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>1</v>
+          <t>CASTILLA 20 LEGANES ASCENSOR CONSULTA Y LIC 19-03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO CASTILLA 20 LEGANES CONSULTA FAIN.docx</t>
+        </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>CASTILLA 20 LEGANES ASCENSOR CONSULTA Y LIC 19-03-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO CASTILLA 20 LEGANES CONSULTA FAIN.docx</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>importes alternativos: consulta previa 1.000 (solo si no se encarga el proyecto) o proyecto+licencia+DF+CFO 5.500 conjunto (la consulta no se cobra); total null por ser alternativos</t>
         </is>
       </c>
-      <c r="U26" s="2" t="n"/>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr"/>
-      <c r="X26" s="4" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2937,7 +2705,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>la hoja es POSTERIOR a la firmada; el documento se tocó DESPUÉS de llegar firmada; la misma enviada sirve a 2 firmadas; 2 hojas de Monday en esa dirección</t>
+          <t>la hoja es POSTERIOR a la firmada; el documento se tocó DESPUÉS de llegar firmada; la misma enviada sirve a 2 firmadas</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2981,43 +2749,33 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 18906409
-CSS  · enviada_comunidad · 2026-01-08 · id 6f76c3eb</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>2</v>
+          <t>AV PRESIDENTE CARMONA 5D MADRID 21-03-2025  pry y df_FIRMADO(1).pdf</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>AV PRESIDENTE CARMONA 5 ESC D MADRID - 08/01/2026 - CSS</t>
+        </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE CARMONA 5D MADRID 21-03-2025  pry y df_FIRMADO(1).pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE CARMONA 5 ESC D MADRID - 08/01/2026 - CSS</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
-      <c r="T27" s="2" t="n"/>
-      <c r="U27" s="2" t="n"/>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr"/>
-      <c r="X27" s="4" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3025,16 +2783,12 @@
           <t>026</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2025-03-26</t>
@@ -3078,40 +2832,35 @@
           <t>50% a la contratación en concepto de provisión de fondos, 50% a la entrega de proyecto</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="n">
-        <v>0</v>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>AV DEL OESTE 1-3 ALCORCON bajada a cota cero 26-03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>AV DEL OESTE 1-3 ALCORCON COTA CERO PRY COINSA 25-03-2025.docx</t>
+        </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>AV DEL OESTE 1-3 ALCORCON bajada a cota cero 26-03-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>AV DEL OESTE 1-3 ALCORCON COTA CERO PRY COINSA 25-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 4.000; dirección con dos números (1-3)</t>
         </is>
       </c>
-      <c r="U28" s="2" t="n"/>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr"/>
-      <c r="X28" s="4" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3171,38 +2920,29 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION, CSS · devuelta_firmada · 2000-01-01 · id 022109b5</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>1</v>
+          <t>FLORIDA 32 ARANJUEZ - CODIGOS DE PEDIDO desglose 02-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>HOJA ENCARGO florida 32 aranjuez SUBVENCION fijo pry propio.pdf</t>
+        </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>FLORIDA 32 ARANJUEZ - CODIGOS DE PEDIDO desglose 02-04-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>HOJA ENCARGO florida 32 aranjuez SUBVENCION fijo pry propio.pdf</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
-      <c r="T29" s="2" t="n"/>
-      <c r="U29" s="2" t="n"/>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3210,16 +2950,12 @@
           <t>028</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
@@ -3264,40 +3000,35 @@
           <t>50% a la contratación en concepto de provisión de fondos, 50% a la entrega del Proyecto</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>NAZARET 14 FUENLABRADA ASCENSOR DF Y CSS 23-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>NAZARET 14 FUENLABRADA ASCENSOR 07-04-2025.docx</t>
+        </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>NAZARET 14 FUENLABRADA ASCENSOR DF Y CSS 23-04-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>NAZARET 14 FUENLABRADA ASCENSOR 07-04-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>PROYECTO Y DIRECCIÓN FACULTATIVA 3.753,40 conjunto (toma de datos, proyecto, licencia, DF y CFO)</t>
         </is>
       </c>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr"/>
-      <c r="X30" s="4" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3359,42 +3090,33 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO · devuelta_firmada · 2000-01-01 · id 0837fae4</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>1</v>
+          <t>CAMARENA 75 MADRID ASCENSOR SCHINDLER 28-05-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>CAMARENA 75 MADRID HOJA DE ENCARGO ASCENSOR 27-03-2025.docx</t>
+        </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>CAMARENA 75 MADRID ASCENSOR SCHINDLER 28-05-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>CAMARENA 75 MADRID HOJA DE ENCARGO ASCENSOR 27-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 030 (duplicado); precio conjunto 3.600; 'cambio completo de dos ascensores' casado a Modificación asc. (dudoso)</t>
         </is>
       </c>
-      <c r="U31" s="2" t="n"/>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr"/>
-      <c r="X31" s="4" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3456,42 +3178,33 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO · devuelta_firmada · 2000-01-01 · id 0837fae4</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>1</v>
+          <t>CAMARENA 75 MADRID SCHINDLER OC 28-05-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>CAMARENA 75 MADRID HOJA DE ENCARGO ASCENSOR 27-03-2025.docx</t>
+        </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>CAMARENA 75 MADRID SCHINDLER OC 28-05-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>CAMARENA 75 MADRID HOJA DE ENCARGO ASCENSOR 27-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 029 (duplicado); precio conjunto 3.600; 'cambio completo de dos ascensores' casado a Modificación asc. (dudoso)</t>
         </is>
       </c>
-      <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3546,42 +3259,33 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>informe final de obra de reparación de cornisa · devuelta_firmada · 2025-06-02 · id 9807d7f7</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>1</v>
+          <t>CAMINO DE LOS VINATEROS 138 MADRID informe pericial 03-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>CAMINO DE LOS VINATEROS 138 MADRID- 02/06/2025 - INFORME FIN DE OBRA CORNISA</t>
+        </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>CAMINO DE LOS VINATEROS 138 MADRID informe pericial 03-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>CAMINO DE LOS VINATEROS 138 MADRID- 02/06/2025 - INFORME FIN DE OBRA CORNISA</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="n"/>
-      <c r="U33" s="2" t="n"/>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3640,42 +3344,33 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS · devuelta_firmada · 2000-01-01 · id 0f123eb2</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>1</v>
+          <t>ENCOMIENDA DE PALACIOS 320 MADRID ascensor PRY+CSS 04-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>ENCOMIENDA DE PALACIOS 320 MADRID ascensor PRY+CSS.docx</t>
+        </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ENCOMIENDA DE PALACIOS 320 MADRID ascensor PRY+CSS 04-06-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>ENCOMIENDA DE PALACIOS 320 MADRID ascensor PRY+CSS.docx</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>proyecto+licencia+DF+CFO a precio conjunto de 3.500; en la casilla CIF pone la razón social</t>
         </is>
       </c>
-      <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr"/>
-      <c r="X34" s="4" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3734,42 +3429,33 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS · devuelta_firmada · 2000-01-01 · id 63a51685</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>1</v>
+          <t>SIENA 55 MADRID ascensor PRY+CSS 04-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>SIENA 55 MADIRD ascensor PRY+CSS.docx</t>
+        </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>SIENA 55 MADRID ascensor PRY+CSS 04-06-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>SIENA 55 MADIRD ascensor PRY+CSS.docx</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>proyecto+licencia+DF+CFO a precio conjunto de 3.500; municipio mal escrito (MADIRD); en la casilla CIF pone la razón social</t>
         </is>
       </c>
-      <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr"/>
-      <c r="X35" s="4" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3824,42 +3510,33 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, SUBVENCION · devuelta_firmada · 2000-01-01 · id 7d425d21</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>1</v>
+          <t>CAÑADA 46 MADRID SUBVENCIONES RENOVACION 10-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>CAÑADA 46 MADRID RENOVACION SUBV 23-01-2025.docx</t>
+        </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>CAÑADA 46 MADRID SUBVENCIONES RENOVACION 10-06-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>CAÑADA 46 MADRID RENOVACION SUBV 23-01-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>oferta especial de renovación consecutiva (no es primera presentación); sin cabecera de empresa</t>
         </is>
       </c>
-      <c r="U36" s="2" t="n"/>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr"/>
-      <c r="X36" s="4" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3914,46 +3591,37 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id c4f27335</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>1</v>
+          <t>IMAGEN 32 MADRID SUBV EXTERNA 11-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>IMAGEN 32 MADRID - 03/06/2025 - SUB CAM25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>IMAGEN 32 MADRID SUBV EXTERNA 11-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>IMAGEN 32 MADRID - 03/06/2025 - SUB CAM25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
           <t>Dirección sin municipio en la hoja (el título dice Madrid)</t>
         </is>
       </c>
-      <c r="U37" s="2" t="n"/>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr"/>
-      <c r="X37" s="4" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4010,46 +3678,37 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-12 · id 326e3ff6</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>1</v>
+          <t>VIRGEN DE LA OLIVA 47 MADRID SUBV PROY EXTERNO 12-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>VIRGEN DE LA OLIVA 47 MADRID - 12/06/2025 - SUBV PRY EXT</t>
+        </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA OLIVA 47 MADRID SUBV PROY EXTERNO 12-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA OLIVA 47 MADRID - 12/06/2025 - SUBV PRY EXT</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto: tramo fijo 2.225 para subvenciones + IEE + LEE, sin desglose</t>
         </is>
       </c>
-      <c r="U38" s="2" t="n"/>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr"/>
-      <c r="X38" s="4" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4116,42 +3775,33 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SATE + ASC · PROYECTO, DIR. OBRA, CSS, SUBVENCION · anulada · 2000-01-01 · id fbfc7260</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>1</v>
+          <t>PLATINO 36 MADRID SATE DF CSS SUBV con CAES 13-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>PLATINO 36 MADRID ASC+ SATE SUBV CON CESION CAES 31-03-2025.docx</t>
+        </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>PLATINO 36 MADRID SATE DF CSS SUBV con CAES 13-06-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>PLATINO 36 MADRID ASC+ SATE SUBV CON CESION CAES 31-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>cabecera solo dice envolvente térmica pero el desglose cobra también proyecto de ascensor; honorarios rebajados a cambio de cesión de CAEs (descuento sin importe); subvenciones 'a éxito' pero con importe fijo 1.980</t>
         </is>
       </c>
-      <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr"/>
-      <c r="X39" s="4" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4204,42 +3854,33 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id 1c6cea75</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>1</v>
+          <t>ALBERTO AGUILERA 68 MADRID SUBV EXTERNA A EXITO 17-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Alberto Aguilera, 68 Madrid - 03/06/2025 - tra subvencion</t>
+        </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ALBERTO AGUILERA 68 MADRID SUBV EXTERNA A EXITO 17-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Alberto Aguilera, 68 Madrid - 03/06/2025 - tra subvencion</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="n"/>
-      <c r="U40" s="2" t="n"/>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr"/>
-      <c r="X40" s="4" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4292,46 +3933,37 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id 26dc27b7</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>1</v>
+          <t>AMANIEL 34 MADRID SUBV EXTERNA A EXITO 17-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Amaniel, 34 - 03/06/2025 - TRA SUBVENCIONES</t>
+        </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>AMANIEL 34 MADRID SUBV EXTERNA A EXITO 17-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Amaniel, 34 - 03/06/2025 - TRA SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
           <t>Solo tramo variable 3,5%, sin tramo fijo; dirección sin municipio</t>
         </is>
       </c>
-      <c r="U41" s="2" t="n"/>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr"/>
-      <c r="X41" s="4" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4396,46 +4028,37 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>instalación de ascensor · devuelta_firmada · 2025-06-12 · id 2701794f</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>1</v>
+          <t>ALHELI 6 LEGANES ASC DF CSS SUBV 19-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>ALHELÍ 6 LEGANES - 12/06/2025 - PRY+SUBV FAIN</t>
+        </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ALHELI 6 LEGANES ASC DF CSS SUBV 19-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>ALHELÍ 6 LEGANES - 12/06/2025 - PRY+SUBV FAIN</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
           <t>Honorarios de proyecto 7.092 conjuntos sin desglose; IEE/LEE/CEE/consulta sin precio y no se sabe si van en proyecto o subvención; total_base = 7.092 + 1.980; título dice FAIN (posible ascensorista pagador)</t>
         </is>
       </c>
-      <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr"/>
-      <c r="X42" s="4" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4498,42 +4121,33 @@
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id a98f945c</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>1</v>
+          <t>AV MARQUES DE CORBERA 32B MADRID PRY ASC CSS Y SUBV 19-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>AV MARQUES DE CORBERA 32B MADRID HE ASCENSOR Y SUBV 05-05-2025.docx</t>
+        </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>AV MARQUES DE CORBERA 32B MADRID PRY ASC CSS Y SUBV 19-06-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>AV MARQUES DE CORBERA 32B MADRID HE ASCENSOR Y SUBV 05-05-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>dos hojas en un fichero (proyecto 5.900 a precio conjunto y subvenciones 1.980); total 7.880 sumado</t>
         </is>
       </c>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr"/>
-      <c r="X43" s="4" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4541,16 +4155,12 @@
           <t>042</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2025-06-23</t>
@@ -4590,44 +4200,39 @@
           <t>A la contratación 100% tramo fijo; a la concesión de cada subvención tramo variable 3,5% del importe concedido tras su ingreso</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="n">
-        <v>0</v>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>CASTILLEJOS 23 FUENLABRADA - 23-06-2025 - RENOVACION SUBV.pdf</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>CASTILLEJOS 23 FUENLABRADA - 23/06/2025 - RENOVACION SUBV</t>
+        </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>CASTILLEJOS 23 FUENLABRADA - 23-06-2025 - RENOVACION SUBV.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>CASTILLEJOS 23 FUENLABRADA - 23/06/2025 - RENOVACION SUBV</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
           <t>Es renovación de subvenciones (encargo previo)</t>
         </is>
       </c>
-      <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W44" s="2" t="inlineStr"/>
-      <c r="X44" s="4" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4682,46 +4287,37 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id 8ed1d2f4</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>1</v>
+          <t>PEDRO LABORDE 58 MADRID SUBV EXTERNA 26-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>PEDRO LABORDE 58 MADRID   - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LABORDE 58 MADRID SUBV EXTERNA 26-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LABORDE 58 MADRID   - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
           <t>La dirección no lleva municipio. El 3,5% variable solo aparece en la forma de pago, no en el total.</t>
         </is>
       </c>
-      <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W45" s="2" t="inlineStr"/>
-      <c r="X45" s="4" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4776,46 +4372,37 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id 7e3b4b9c</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>1</v>
+          <t>SIERRA DEL VALLE 52 MADRID SUBV EXTERNA 27-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>SIERRA DEL VALLE 52 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>SIERRA DEL VALLE 52 MADRID SUBV EXTERNA 27-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>SIERRA DEL VALLE 52 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
           <t>Dirección sin municipio en la hoja (el título dice Madrid)</t>
         </is>
       </c>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr"/>
-      <c r="X46" s="4" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4870,46 +4457,37 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id d9c4e200</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>1</v>
+          <t>CASABERMEJA 2 MADRID SUBVENCION EXTERNA 30-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>CASABERMEJA 2 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>CASABERMEJA 2 MADRID SUBVENCION EXTERNA 30-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>CASABERMEJA 2 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
           <t>Dirección sin municipio en la hoja (el título dice Madrid)</t>
         </is>
       </c>
-      <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr"/>
-      <c r="X47" s="4" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4968,46 +4546,37 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>instalación de ascensor · devuelta_firmada · 2025-06-27 · id 371d5984</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>1</v>
+          <t>LLANOS DE ESCUDERO 8 MADRID ASCENSOR ROSERSESE 30-06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>LLANOS DE ESCUDERO 8 MADRID - 27/06/2025 - PRY ROSERSESE</t>
+        </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>LLANOS DE ESCUDERO 8 MADRID ASCENSOR ROSERSESE 30-06-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>LLANOS DE ESCUDERO 8 MADRID - 27/06/2025 - PRY ROSERSESE</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr"/>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.500 conjunto para redacción + licencia + fin de obra + DF, sin desglose; título menciona ROSERSESE</t>
         </is>
       </c>
-      <c r="U48" s="2" t="n"/>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr"/>
-      <c r="X48" s="4" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5015,16 +4584,12 @@
           <t>047</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2025-07-07</t>
@@ -5065,44 +4630,39 @@
           <t>A la contratación 100% mediante cargo en cuenta</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="n">
-        <v>0</v>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>BILBAO 1 ALCORCON SOLO IEE 07-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>BILBAO 1 ALCORCON - 02/07/2025 - IEE</t>
+        </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>BILBAO 1 ALCORCON SOLO IEE 07-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>BILBAO 1 ALCORCON - 02/07/2025 - IEE</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr"/>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 850 para IEE + CEE; no se reparte.</t>
         </is>
       </c>
-      <c r="U49" s="2" t="n"/>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W49" s="2" t="inlineStr"/>
-      <c r="X49" s="4" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5157,46 +4717,37 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id d233f5bc</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>1</v>
+          <t>CARLOS MARTIN ALVAREZ 104 MADRID SUBV EXTERNA 07-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>CARLOS MARTIN ALVAREZ 104 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>CARLOS MARTIN ALVAREZ 104 MADRID SUBV EXTERNA 07-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>CARLOS MARTIN ALVAREZ 104 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr"/>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
           <t>Dirección sin municipio en la hoja (el título dice Madrid)</t>
         </is>
       </c>
-      <c r="U50" s="2" t="n"/>
-      <c r="V50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W50" s="2" t="inlineStr"/>
-      <c r="X50" s="4" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5204,16 +4755,12 @@
           <t>049</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2025-07-07</t>
@@ -5254,40 +4801,35 @@
           <t>A la contratación 100% mediante cargo en cuenta</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="n">
-        <v>0</v>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>PRINCESA 25 ALCORCON SOLO IEE 07-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>PRINCESA 25 ALCORCON - 02/07/2025 - IEE</t>
+        </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>PRINCESA 25 ALCORCON SOLO IEE 07-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>PRINCESA 25 ALCORCON - 02/07/2025 - IEE</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
-      <c r="T51" s="2" t="n"/>
-      <c r="U51" s="2" t="n"/>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr"/>
-      <c r="X51" s="4" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5342,46 +4884,37 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id 63120043</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>1</v>
+          <t>SIERRA DE MOLINA 11 MADRID SUBV EXTERNA 07-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>SIERRA DE MOLINA 11 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>SIERRA DE MOLINA 11 MADRID SUBV EXTERNA 07-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>SIERRA DE MOLINA 11 MADRID - 03/06/2025 - SUBV CAM 25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
           <t>Dirección sin municipio en la hoja (el título dice Madrid)</t>
         </is>
       </c>
-      <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W52" s="2" t="inlineStr"/>
-      <c r="X52" s="4" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5389,16 +4922,12 @@
           <t>051</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2025-07-07</t>
@@ -5439,44 +4968,39 @@
           <t>A la contratación 100% mediante cargo en cuenta</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="n">
-        <v>0</v>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>VIRGEN DE ICIAR 22 ALCORCON SOLO IEE 07-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>VIRGEN DE ICIAR 22 ALCORCON - 02/07/2025 - IEE</t>
+        </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>VIRGEN DE ICIAR 22 ALCORCON SOLO IEE 07-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>VIRGEN DE ICIAR 22 ALCORCON - 02/07/2025 - IEE</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 850 para IEE + CEE; no se reparte.</t>
         </is>
       </c>
-      <c r="U53" s="2" t="n"/>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr"/>
-      <c r="X53" s="4" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5540,46 +5064,37 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>instalación de ascensor · devuelta_firmada · 2025-06-25 · id 1b41751d</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>1</v>
+          <t>GUANCHA 1 MADRID ASC DF CSS Y SUBV 08-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>GUANCHA 1 MADRID - 25/06/2025 - PRY+SUBV</t>
+        </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>GUANCHA 1 MADRID ASC DF CSS Y SUBV 08-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>GUANCHA 1 MADRID - 25/06/2025 - PRY+SUBV</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
           <t>Honorarios de proyecto 5.900 conjuntos sin desglose; IEE/LEE/CEE sin precio, no se sabe si van en proyecto o subvención; subvención sin tramo variable; total_base = 5.900 + 1.980</t>
         </is>
       </c>
-      <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="4" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5642,46 +5157,37 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>instalación de ascensor con derribo de escalera · devuelta_firmada · 2025-07-02 · id 0bdaeb58</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>1</v>
+          <t>FRAY JOSE CERDEIRIÑA 66 MADRID CEGA ASCENSOR Y SUBV 11-07-2025.PDF</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>FRAY JOSÉ CERDEIRIÑA 66 MADRID - 07/07/2025 - PRY+SUBV</t>
+        </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>FRAY JOSE CERDEIRIÑA 66 MADRID CEGA ASCENSOR Y SUBV 11-07-2025.PDF</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>FRAY JOSÉ CERDEIRIÑA 66 MADRID - 07/07/2025 - PRY+SUBV</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
           <t>Ascensor con derribo de escalera; proyecto 5.000 conjunto sin desglose; IEE/CEE sin precio, no se sabe si en proyecto o subvención; total_base = 5.000 + 1.980</t>
         </is>
       </c>
-      <c r="U55" s="2" t="n"/>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="S55" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W55" s="2" t="inlineStr"/>
-      <c r="X55" s="4" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5744,46 +5250,37 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id a51877e9</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>1</v>
+          <t>NUÑO GOMEZ 16 MADRID CEGA ASCENSOR Y SUBV 11-07-2025.PDF</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>NUÑO GOMEZ 16 MADRID - 07/07/2025 - PRY+SUBV</t>
+        </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>NUÑO GOMEZ 16 MADRID CEGA ASCENSOR Y SUBV 11-07-2025.PDF</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>NUÑO GOMEZ 16 MADRID - 07/07/2025 - PRY+SUBV</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
           <t>Ascensor con derribo de escalera; proyecto 5.000 conjunto sin desglose; IEE/CEE sin precio, no se sabe si en proyecto o subvención; total_base = 5.000 + 1.980</t>
         </is>
       </c>
-      <c r="U56" s="2" t="n"/>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr"/>
-      <c r="X56" s="4" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5846,46 +5343,37 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>instalación de ascensor con derribo de escalera · devuelta_firmada · 2025-07-02 · id 284156a8</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>1</v>
+          <t>VIDRIERIA 3 MADRID CEGA ASCENSOR Y SUBV 11-07-2025.PDF</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>VIDRIERIA 3 MADRID - 07/07/2025 - PRY+SUBV</t>
+        </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>VIDRIERIA 3 MADRID CEGA ASCENSOR Y SUBV 11-07-2025.PDF</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>VIDRIERIA 3 MADRID - 07/07/2025 - PRY+SUBV</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 5.000 es precio conjunto de toma de datos, proyecto, licencia, fin de obra, CSS y DF; IEE y CEE sin precio propio (no queda claro si van en proyecto o en subvención). Ascensor con derribo de escalera.</t>
         </is>
       </c>
-      <c r="U57" s="2" t="n"/>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="S57" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr"/>
-      <c r="X57" s="4" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5940,46 +5428,37 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-06-03 · id e427a8c0</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>1</v>
+          <t>LOPEZ GRASS 42 MADRID SUBV EXTERNA 15-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>LOPEZ GRASS 42 MADRID - 03/06/2025 - SUB CAM25 DEL BRIO</t>
+        </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>LOPEZ GRASS 42 MADRID SUBV EXTERNA 15-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>LOPEZ GRASS 42 MADRID - 03/06/2025 - SUB CAM25 DEL BRIO</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr"/>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
           <t>Dirección sin municipio en la hoja (el título dice Madrid)</t>
         </is>
       </c>
-      <c r="U58" s="2" t="n"/>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr"/>
-      <c r="X58" s="4" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -6038,46 +5517,37 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2025-07-16 · id 473d17d1</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>1</v>
+          <t>PONTEVEDRA 1 MOSTOLES rosersese asc df y css 16-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>PONTEVEDRA 1 MOSTOLES - 16/07/2025 - PRY+CSS</t>
+        </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>PONTEVEDRA 1 MOSTOLES rosersese asc df y css 16-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>PONTEVEDRA 1 MOSTOLES - 16/07/2025 - PRY+CSS</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr"/>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.500 conjunto para redacción + licencia + fin de obra + DF, sin desglose</t>
         </is>
       </c>
-      <c r="U59" s="2" t="n"/>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="S59" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W59" s="2" t="inlineStr"/>
-      <c r="X59" s="4" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -6085,16 +5555,12 @@
           <t>058</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>2 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2025-07-18</t>
@@ -6145,47 +5611,37 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SATE · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id 5c0e8b27
-ENVOLVENTE TÉRMICA · enviada_comunidad · 2025-06-10 · id f8012e25</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>2</v>
+          <t>GONZALO CESPEDES 21 MADRID SATE 18-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>GONZALO DE CESPEDES 21 MADRID - 10/06/2025 - SATE SIN CAES ROEN</t>
+        </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>GONZALO CESPEDES 21 MADRID SATE 18-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>GONZALO DE CESPEDES 21 MADRID - 10/06/2025 - SATE SIN CAES ROEN</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr"/>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
           <t>La hoja dice 'ENVOLVENTE TÉRMICA' (título: SATE SIN CAES ROEN), casado como SATE envolvente completa; precio conjunto 8.360 incluida la subvención, sin tramo variable</t>
         </is>
       </c>
-      <c r="U60" s="2" t="n"/>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr"/>
-      <c r="X60" s="4" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -6193,16 +5649,12 @@
           <t>059</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2025-07-24</t>
@@ -6255,47 +5707,37 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SATE + ASC · PROYECTO, DIR. OBRA, CSS, SUBVENCION · devuelta_firmada · 2000-01-01 · id 17baee84
-ENVOLVENTE TERMICA E INSTALACION DE ASCENSOR MAS TRAMITACION DE SUBVENCIONES · enviada_comunidad · 2025-07-18 · id ebc347a3</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>2</v>
+          <t>HACIENDA PAVONES 222 MADRID SATE+ASC+SUBV 24-07-2025 cobrar en octubre.pdf</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>HACIENDA PAVONES 222 MADRID - 18/07/2025 - SATE+ASC+SUBV</t>
+        </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>HACIENDA PAVONES 222 MADRID SATE+ASC+SUBV 24-07-2025 cobrar en octubre.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>HACIENDA PAVONES 222 MADRID - 18/07/2025 - SATE+ASC+SUBV</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr"/>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 10.000 para todo; no se reparte. 'Envolvente térmica' casado como SATE envolvente completa (la hoja no dice SATE, solo el título).</t>
         </is>
       </c>
-      <c r="U61" s="2" t="n"/>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="S61" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W61" s="2" t="inlineStr"/>
-      <c r="X61" s="4" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6354,46 +5796,37 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2025-07-30 · id be9cbf7e</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>1</v>
+          <t>JESUS 40 ARANJUEZ PRY+CSS 31-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>JESUS 40 ARANJUEZ - 30/07/2025 - PRY+CSS</t>
+        </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>JESUS 40 ARANJUEZ PRY+CSS 31-07-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>JESUS 40 ARANJUEZ - 30/07/2025 - PRY+CSS</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.500 conjunto para redacción + licencia + fin de obra + DF, sin desglose</t>
         </is>
       </c>
-      <c r="U62" s="2" t="n"/>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr"/>
-      <c r="X62" s="4" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6449,42 +5882,33 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>IEE · devuelta_firmada · 2025-08-25 · id 6900b731</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>1</v>
+          <t>BENIMAMET 59 SOLO IEE - CP BENIMAMET 59 - 29-08-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>BENIMAMET 59 MADRID - 25/08/2025 - IEE</t>
+        </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>BENIMAMET 59 SOLO IEE - CP BENIMAMET 59 - 29-08-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>BENIMAMET 59 MADRID - 25/08/2025 - IEE</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
-      <c r="T63" s="2" t="n"/>
-      <c r="U63" s="2" t="n"/>
-      <c r="V63" s="2" t="inlineStr">
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="n"/>
+      <c r="S63" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr"/>
-      <c r="X63" s="4" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6544,46 +5968,37 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SALVAESCALERAS · devuelta_firmada · 2025-08-29 · id 03e708c0</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>1</v>
+          <t>MONTEJURRA 33 MADRID PRY SALVAESCALERAS_signed 01-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>MONTEJURRA 33 MADRID - 29/08/2025 - PRY SALVAESCALERAS</t>
+        </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>MONTEJURRA 33 MADRID PRY SALVAESCALERAS_signed 01-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>MONTEJURRA 33 MADRID - 29/08/2025 - PRY SALVAESCALERAS</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr"/>
-      <c r="T64" s="2" t="inlineStr">
-        <is>
           <t>La hoja dice 'SALVAESCALERAS', casado como Plataforma; arquitectura 2.500 conjunta sin desglose; CSS sin forma de pago propia</t>
         </is>
       </c>
-      <c r="U64" s="2" t="n"/>
-      <c r="V64" s="2" t="inlineStr">
+      <c r="S64" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W64" s="2" t="inlineStr"/>
-      <c r="X64" s="4" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6591,16 +6006,12 @@
           <t>063</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -6644,44 +6055,39 @@
           <t>A la contratación, en concepto de provisión de fondos: 50% del total de los honorarios. A la entrega del Proyecto: 50% restante.</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="n">
-        <v>0</v>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCA DELGADO 7 ALCOBENDAS - SUSTITUCION 7 ASCENSORES 03-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCA DELGADO 7 ALCOBENDAS - 03/09/2025 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCA DELGADO 7 ALCOBENDAS - SUSTITUCION 7 ASCENSORES 03-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCA DELGADO 7 ALCOBENDAS - 03/09/2025 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="inlineStr"/>
-      <c r="T65" s="2" t="inlineStr">
-        <is>
           <t>Sustitución de 7 ascensores casado como Modificación asc. Precio conjunto 14.000; no se reparte.</t>
         </is>
       </c>
-      <c r="U65" s="2" t="n"/>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="S65" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr"/>
-      <c r="X65" s="4" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6744,46 +6150,37 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>BAJADA A COTA CERO · devuelta_firmada · 2025-07-11 · id d376f770</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>1</v>
+          <t>RONDA DE SEGOVIA 29 MADRID PRY COTA CERO + SUBV 03-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>RONDA DE SEGOVIA 29 MADRID - 03/09/2025 - PRY + SUBV</t>
+        </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>RONDA DE SEGOVIA 29 MADRID PRY COTA CERO + SUBV 03-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>RONDA DE SEGOVIA 29 MADRID - 03/09/2025 - PRY + SUBV</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="inlineStr"/>
-      <c r="T66" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 4.500 incluida la subvención (que tiene forma de pago propia pero sin importe propio)</t>
         </is>
       </c>
-      <c r="U66" s="2" t="n"/>
-      <c r="V66" s="2" t="inlineStr">
+      <c r="S66" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W66" s="2" t="inlineStr"/>
-      <c r="X66" s="4" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6842,46 +6239,37 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCION DE 7 ASCENSORES · devuelta_firmada · 2025-07-31 · id 07e42be9</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>1</v>
+          <t>MIRADOR DEL PARDO 7 LAS ROZAS - ASCENSORES 04-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>MIRADOR DEL PARDO 7 LAS ROZAS - 04/09/2025 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>MIRADOR DEL PARDO 7 LAS ROZAS - ASCENSORES 04-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>MIRADOR DEL PARDO 7 LAS ROZAS - 04/09/2025 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr"/>
-      <c r="T67" s="2" t="inlineStr">
-        <is>
           <t>Sustitución de 7 ascensores, casado como Modificación asc.; precio conjunto 7.000</t>
         </is>
       </c>
-      <c r="U67" s="2" t="n"/>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="S67" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr"/>
-      <c r="X67" s="4" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6944,46 +6332,37 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2025-09-09 · id 35ee154d</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>1</v>
+          <t>BERASTEGUI 33 MADRID - PRY ASC- 9-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>BERASTEGUI 33 MADRID - 09/09/2025 - PRY ASC</t>
+        </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>BERASTEGUI 33 MADRID - PRY ASC- 9-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>BERASTEGUI 33 MADRID - 09/09/2025 - PRY ASC</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.500 conjunto para redacción + licencia + fin de obra + DF, sin desglose</t>
         </is>
       </c>
-      <c r="U68" s="2" t="n"/>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="S68" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr"/>
-      <c r="X68" s="4" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -7046,46 +6425,37 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2025-09-09 · id 35ee154d</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>1</v>
+          <t>BERASTEGUI 33 MADRID ascensor 09-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>BERASTEGUI 33 MADRID - 09/09/2025 - PRY ASC</t>
+        </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>BERASTEGUI 33 MADRID ascensor 09-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>BERASTEGUI 33 MADRID - 09/09/2025 - PRY ASC</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.500 es precio conjunto de proyecto, licencia, fin de obra y DF; no se reparte.</t>
         </is>
       </c>
-      <c r="U69" s="2" t="n"/>
-      <c r="V69" s="2" t="inlineStr">
+      <c r="S69" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W69" s="2" t="inlineStr"/>
-      <c r="X69" s="4" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7141,46 +6511,37 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2025-07-30 · id 11d15b4b</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>1</v>
+          <t>RIO DUERO 65 LEGANES - SUBV EXTERNA 09-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>RIO DUERO 65 LEGANES - 30/07/2025 - TRA SUBVENCION</t>
+        </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>RIO DUERO 65 LEGANES - SUBV EXTERNA 09-09-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>RIO DUERO 65 LEGANES - 30/07/2025 - TRA SUBVENCION</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 2.225 para subvención + IEE, sin desglose</t>
         </is>
       </c>
-      <c r="U70" s="2" t="n"/>
-      <c r="V70" s="2" t="inlineStr">
+      <c r="S70" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr"/>
-      <c r="X70" s="4" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -7251,42 +6612,33 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SATE + ACCESIB · PROYECTO, CEE, DIR. OBRA, IEE, LIBRO, SUBVENCION · devuelta_firmada · 2000-01-01 · id 6673622f</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="n">
-        <v>1</v>
+          <t>PLAZA LUCA DE TENA 11 MADRID PRY - SATE (CON CESION CAES)- ACCESIB - LE - IEE - SUBV - 18-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>PLAZA LUCA DE TENA 11 MADRID SATE CON CESION CAES 26-06-2025.docx</t>
+        </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>PLAZA LUCA DE TENA 11 MADRID PRY - SATE (CON CESION CAES)- ACCESIB - LE - IEE - SUBV - 18-09-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>PLAZA LUCA DE TENA 11 MADRID SATE CON CESION CAES 26-06-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
           <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr">
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr">
         <is>
           <t>los conceptos suman 18.880 pero la hoja dice 18.800 sin descuento; descuento de 8.600 por cesión de CAES (total con descuento 10.200, condicionado a firmar la cesión); además 3,5% a éxito en subvenciones; licencia, CEE y DF descritos sin precio propio</t>
         </is>
       </c>
-      <c r="U71" s="2" t="n"/>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="S71" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr"/>
-      <c r="X71" s="4" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7341,46 +6693,37 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>ESTUDIO TECNICO DE SUSTITUICÓN DE VIGA ESTRUCTURAL · devuelta_firmada · 2025-10-01 · id f4b29447</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="n">
-        <v>1</v>
+          <t>ISLA CRISTINA 1 ARROYOMOLINOS SUST DE VIGA 02-10-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>ISLA CRISTINA 1 ARROYOMOLINOS - 01/10/2025 - ESTUDIO TECNICO FAIN</t>
+        </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ISLA CRISTINA 1 ARROYOMOLINOS SUST DE VIGA 02-10-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>ISLA CRISTINA 1 ARROYOMOLINOS - 01/10/2025 - ESTUDIO TECNICO FAIN</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr">
-        <is>
           <t>Estudio técnico de sustitución de viga estructural: se describe como memoria técnica + planos para DR, dudoso entre MEMORIA TECNICA e INFORME PERICIAL; título dice FAIN (posible ascensorista pagador)</t>
         </is>
       </c>
-      <c r="U72" s="2" t="n"/>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="S72" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr"/>
-      <c r="X72" s="4" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -7439,42 +6782,33 @@
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, SUBVENCION · devuelta_firmada · 2000-01-01 · id c4314750</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="n">
-        <v>1</v>
+          <t>VICENTE CAMARON 1 MADRID PRY + ASC 06-10-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO vicente camaron 1 madrid ASCENSOR Y SUBV.docx</t>
+        </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>VICENTE CAMARON 1 MADRID PRY + ASC 06-10-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO vicente camaron 1 madrid ASCENSOR Y SUBV.docx</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr">
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 072 (duplicado); dos hojas en un fichero (proyecto 6.000 y subvenciones 1.980); total 7.980 sumado; la línea de 4.260 agrupa toma de datos, proyecto, visado y dirección de obra</t>
         </is>
       </c>
-      <c r="U73" s="2" t="n"/>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="S73" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr"/>
-      <c r="X73" s="4" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7533,42 +6867,33 @@
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA, SUBVENCION · devuelta_firmada · 2000-01-01 · id c4314750</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="n">
-        <v>1</v>
+          <t>VICENTE CAMARON 1 MADRID SUBV 06-10-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO vicente camaron 1 madrid ASCENSOR Y SUBV.docx</t>
+        </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>VICENTE CAMARON 1 MADRID SUBV 06-10-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO vicente camaron 1 madrid ASCENSOR Y SUBV.docx</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr"/>
-      <c r="S74" s="2" t="inlineStr"/>
-      <c r="T74" s="2" t="inlineStr">
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
         <is>
           <t>texto idéntico a 071 (duplicado); dos hojas en un fichero (proyecto 6.000 y subvenciones 1.980); total 7.980 sumado; la línea de 4.260 agrupa toma de datos, proyecto, visado y dirección de obra</t>
         </is>
       </c>
-      <c r="U74" s="2" t="n"/>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="S74" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr"/>
-      <c r="X74" s="4" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7638,46 +6963,37 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA Y ASCENSOR · devuelta_firmada · 2025-09-17 · id cf50cfa1</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="n">
-        <v>1</v>
+          <t>CANCION DEL OLVIDO 33 MADRID PRY SATE+ASC+SUBV CP 15-10-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>CANCION DEL OLVIDO 33 MADRID - 17/09/2025 - SATE+ASC CON CAES</t>
+        </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>CANCION DEL OLVIDO 33 MADRID PRY SATE+ASC+SUBV CP 15-10-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>CANCION DEL OLVIDO 33 MADRID - 17/09/2025 - SATE+ASC CON CAES</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="S75" s="2" t="inlineStr"/>
-      <c r="T75" s="2" t="inlineStr">
-        <is>
           <t>Envolvente térmica casada como SATE; SATE 8.500 tras descuento por CAES de 6.430 sobre 14.930 (proyecto 11.000 + LE 1.300 + IEE 650 + subvención 1.980); la línea de 8.500 pone 'iva' sin '+'; ascensor 6.500 aparte; dudoso si el bloque es SATE + ASCENSOR CON CESION DE CAES</t>
         </is>
       </c>
-      <c r="U75" s="2" t="n"/>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="S75" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr"/>
-      <c r="X75" s="4" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7740,42 +7056,33 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO · devuelta_firmada · 2000-01-01 · id 0da537af</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="n">
-        <v>1</v>
+          <t>JUAN TORNERO 62 HE ELEVADOR IBERLEAN 15-10-2025.docx.pdf</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>JUAN TORNERO 62 HE ELEVADOR IBERLEAN 15-10-2025.docx</t>
+        </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>JUAN TORNERO 62 HE ELEVADOR IBERLEAN 15-10-2025.docx.pdf</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>JUAN TORNERO 62 HE ELEVADOR IBERLEAN 15-10-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr"/>
-      <c r="S76" s="2" t="inlineStr"/>
-      <c r="T76" s="2" t="inlineStr">
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr">
         <is>
           <t>precio conjunto 3.736; 'elevador' sin casar (ascensor o plataforma); el conforme dice 'cliente', no consta que sea la comunidad</t>
         </is>
       </c>
-      <c r="U76" s="2" t="n"/>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="S76" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr"/>
-      <c r="X76" s="4" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7835,42 +7142,33 @@
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 3ff985f3</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="n">
-        <v>1</v>
+          <t>PIEDRAHITA 2 MADRID ASC 28-10-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>PIEDRAHITA 2 MADRID HE ASCENSOR Y SUBV 11-03-2025.docx</t>
+        </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>PIEDRAHITA 2 MADRID ASC 28-10-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>PIEDRAHITA 2 MADRID HE ASCENSOR Y SUBV 11-03-2025.docx</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr"/>
-      <c r="S77" s="2" t="inlineStr"/>
-      <c r="T77" s="2" t="inlineStr">
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr">
         <is>
           <t>dos hojas en un fichero (proyecto 6.000 y subvenciones 1.980); total 7.980 sumado; la línea de 4.260 agrupa toma de datos, proyecto, visado y dirección de obra</t>
         </is>
       </c>
-      <c r="U77" s="2" t="n"/>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="S77" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr"/>
-      <c r="X77" s="4" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7930,38 +7228,29 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SOLO IEE · IEE · devuelta_firmada · 2000-01-01 · id a2f56568</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>1</v>
+          <t>ESTANISLAO FIGUERAS 8 MADRID - IEE 05-11-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO estanislao figueras 8 madrid IEE .docx</t>
+        </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ESTANISLAO FIGUERAS 8 MADRID - IEE 05-11-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO estanislao figueras 8 madrid IEE .docx</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R78" s="2" t="inlineStr"/>
-      <c r="S78" s="2" t="inlineStr"/>
-      <c r="T78" s="2" t="n"/>
-      <c r="U78" s="2" t="n"/>
-      <c r="V78" s="2" t="inlineStr">
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="n"/>
+      <c r="S78" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr"/>
-      <c r="X78" s="4" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8026,46 +7315,37 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA  · devuelta_firmada · 2025-10-08 · id 3d4bd10f</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="n">
-        <v>1</v>
+          <t>ALGODRE 2 MADRID SATE 20-11-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>ALGODRE 2 MADRID - 08/10/2025 - SATE CAES</t>
+        </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ALGODRE 2 MADRID SATE 20-11-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>ALGODRE 2 MADRID - 08/10/2025 - SATE CAES</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="S79" s="2" t="inlineStr"/>
-      <c r="T79" s="2" t="inlineStr">
-        <is>
           <t>Importes por concepto son SIN descuento (suman 32.910); descuento por cesión de CAES -15.910 deja total 17.000. Encaja con bloque SATE CON CESION DE CAES. LEE con precio pero no está en el desglose; CEE en desglose sin precio. 'Envolvente térmica' casado como SATE envolvente completa.</t>
         </is>
       </c>
-      <c r="U79" s="2" t="n"/>
-      <c r="V79" s="2" t="inlineStr">
+      <c r="S79" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W79" s="2" t="inlineStr"/>
-      <c r="X79" s="4" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8128,46 +7408,37 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>INSTALACION DE ASCENSOR  · devuelta_firmada · 2025-11-26 · id af0299c9</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>1</v>
+          <t>SEGOVIA 49 MADRID PRY ASC 03-12-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>SEGOVIA 49 MADRID - 26/11/2025 - INS ASCENSOR</t>
+        </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>SEGOVIA 49 MADRID PRY ASC 03-12-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>SEGOVIA 49 MADRID - 26/11/2025 - INS ASCENSOR</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="S80" s="2" t="inlineStr"/>
-      <c r="T80" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 7.900 conjunto sin desglose; IEE y CEE solo si no hay uno previo válido; tramo variable 3% (no 3,5%); total_base = 7.900 + 1.980</t>
         </is>
       </c>
-      <c r="U80" s="2" t="n"/>
-      <c r="V80" s="2" t="inlineStr">
+      <c r="S80" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr"/>
-      <c r="X80" s="4" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8175,16 +7446,12 @@
           <t>079</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>3 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t>2025-12-09</t>
@@ -8236,48 +7503,37 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA  · devuelta_firmada · 2025-10-09 · id 024f6482
-None · borrador · 2026-08-24 · id 68217146
-Instalación de Ascensor Prueba Agosto · borrador · 2026-08-24 · id fe7af39e</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>3</v>
+          <t>ALCARRIA 60 LEGANES PRY SATE 09-12-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>ALCARRIA 60 LEGANES - 09/10/2025 - PRY SATE</t>
+        </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ALCARRIA 60 LEGANES PRY SATE 09-12-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>ALCARRIA 60 LEGANES - 09/10/2025 - PRY SATE</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="inlineStr"/>
-      <c r="T81" s="2" t="inlineStr">
-        <is>
           <t>La hoja dice 'ENVOLVENTE TÉRMICA' (título: PRY SATE), casado como SATE envolvente completa; proyecto 9.800 conjunto; IEE/LEE/CEE sin precio; total_base = 9.800 + 1.980</t>
         </is>
       </c>
-      <c r="U81" s="2" t="n"/>
-      <c r="V81" s="2" t="inlineStr">
+      <c r="S81" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr"/>
-      <c r="X81" s="4" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8342,46 +7598,37 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA · devuelta_firmada · 2025-11-07 · id 03611553</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>1</v>
+          <t>SANCHEZ PRECIADO 40 MADRID SATE 18-12-2025.pdf</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>SÁNCHEZ PRECIADO 40 MADRID - 07/11/2025 - PRY SATE CON CESION DE CAES</t>
+        </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>SANCHEZ PRECIADO 40 MADRID SATE 18-12-2025.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>SÁNCHEZ PRECIADO 40 MADRID - 07/11/2025 - PRY SATE CON CESION DE CAES</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr"/>
-      <c r="T82" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 9.500 con descuento por cesión de CAES (encaja en SATE CON CESION DE CAES, no desglosado); envolvente térmica casada como SATE; IEE/CEE/LEE solo si hacen falta; incluye estimación de obra 450.000 + IVA</t>
         </is>
       </c>
-      <c r="U82" s="2" t="n"/>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="S82" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr"/>
-      <c r="X82" s="4" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8396,7 +7643,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>el documento se tocó DESPUÉS de llegar firmada; la misma enviada sirve a 2 firmadas; 2 hojas de Monday en esa dirección; la lectura avisa de algo raro</t>
+          <t>el documento se tocó DESPUÉS de llegar firmada; la misma enviada sirve a 2 firmadas; la lectura avisa de algo raro</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -8440,47 +7687,37 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 18906409
-CSS  · enviada_comunidad · 2026-01-08 · id 6f76c3eb</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>2</v>
+          <t>AV PRESIDENTE CARMONA 5 ESC D MADRID - 08-01-2026 CSS.pdf</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>AV PRESIDENTE CARMONA 5 ESC D MADRID - 08/01/2026 - CSS</t>
+        </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE CARMONA 5 ESC D MADRID - 08-01-2026 CSS.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE CARMONA 5 ESC D MADRID - 08/01/2026 - CSS</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="S83" s="2" t="inlineStr"/>
-      <c r="T83" s="2" t="inlineStr">
-        <is>
           <t>Duplicado exacto de 025 (mismo DRIVE_ID).</t>
         </is>
       </c>
-      <c r="U83" s="2" t="n"/>
-      <c r="V83" s="2" t="inlineStr">
+      <c r="S83" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W83" s="2" t="inlineStr"/>
-      <c r="X83" s="4" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -8544,46 +7781,37 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>SATE + ACCESIB · PROYECTO, SUBVENCION, CSS, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 24f9569b</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>1</v>
+          <t>PARLA 20 GETAFE PRY SATE + ACCES 13-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>PARLA 20 GETAFE - 27/11/2025 - PRY SATE+SUBV</t>
+        </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>PARLA 20 GETAFE PRY SATE + ACCES 13-01-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>PARLA 20 GETAFE - 27/11/2025 - PRY SATE+SUBV</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="S84" s="2" t="inlineStr"/>
-      <c r="T84" s="2" t="inlineStr">
-        <is>
           <t>Envolvente térmica y mejora de accesibilidad, casado como SATE envolvente completa + Accesibilidad; precio conjunto 8.500; se tramitan los CAES pero no dice si hay descuento por cesión; subvención sin tramo variable</t>
         </is>
       </c>
-      <c r="U84" s="2" t="n"/>
-      <c r="V84" s="2" t="inlineStr">
+      <c r="S84" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr"/>
-      <c r="X84" s="4" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -8638,42 +7866,33 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE FOSO REDUCIDO · devuelta_firmada · 2026-01-22 · id 22e4ebee</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>1</v>
+          <t>MALDONADO 33 MADRID INF FOSO REDUCIDO - 22-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>MALDONADO 33 MADRID - 22/01/2026 - INFORME FOSO REDUCIDO</t>
+        </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>MALDONADO 33 MADRID INF FOSO REDUCIDO - 22-01-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>MALDONADO 33 MADRID - 22/01/2026 - INFORME FOSO REDUCIDO</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R85" s="2" t="inlineStr">
-        <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr"/>
-      <c r="T85" s="2" t="n"/>
-      <c r="U85" s="2" t="n"/>
-      <c r="V85" s="2" t="inlineStr">
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="n"/>
+      <c r="S85" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W85" s="2" t="inlineStr"/>
-      <c r="X85" s="4" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -8732,46 +7951,37 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2026-01-26 · id c2039e1f</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>1</v>
+          <t>INDEPENDENCIA 43 SAN SEBASTIAN DE LOS REYES - PRY ASC - 27-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 43 SAN SEBASTIAN DE LOS REYES - 26/01/2026 - PRY ASC+CSS</t>
+        </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 43 SAN SEBASTIAN DE LOS REYES - PRY ASC - 27-01-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 43 SAN SEBASTIAN DE LOS REYES - 26/01/2026 - PRY ASC+CSS</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="S86" s="2" t="inlineStr"/>
-      <c r="T86" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.500 conjunto para redacción + licencia + fin de obra + DF, sin desglose</t>
         </is>
       </c>
-      <c r="U86" s="2" t="n"/>
-      <c r="V86" s="2" t="inlineStr">
+      <c r="S86" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W86" s="2" t="inlineStr"/>
-      <c r="X86" s="4" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8826,46 +8036,37 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION DE SUBVENCIONES · devuelta_firmada · 2026-01-14 · id 0cf24922</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>1</v>
+          <t>SAN ROQUE 14 MADRID - SUBV - 28-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>SAN ROQUE 14 MADRID - 14/01/2026 - SUBACC</t>
+        </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>SAN ROQUE 14 MADRID - SUBV - 28-01-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>SAN ROQUE 14 MADRID - 14/01/2026 - SUBACC</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="S87" s="2" t="inlineStr"/>
-      <c r="T87" s="2" t="inlineStr">
-        <is>
           <t>IEE y CEE solo si hace falta, sin precio propio indicado.</t>
         </is>
       </c>
-      <c r="U87" s="2" t="n"/>
-      <c r="V87" s="2" t="inlineStr">
+      <c r="S87" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W87" s="2" t="inlineStr"/>
-      <c r="X87" s="4" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -8930,46 +8131,37 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA Y ASCENSOR · anulada · 2026-01-23 · id f8952f4d</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>1</v>
+          <t>ARROYO DE FONTARRON 381 MADRID PRY SATE + ASC + SUBV 02-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>ARROYO DE FONTARRÓN 381 MADRID - 23/01/2026 - PRY ASC+SATE+SUBV</t>
+        </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ARROYO DE FONTARRON 381 MADRID PRY SATE + ASC + SUBV 02-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>ARROYO DE FONTARRÓN 381 MADRID - 23/01/2026 - PRY ASC+SATE+SUBV</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="S88" s="2" t="inlineStr"/>
-      <c r="T88" s="2" t="inlineStr">
-        <is>
           <t>Proyecto conjunto 20.000 (ascensor con derribo de escalera + SATE fachada y renovación de cubierta), sin desglose; casado como SATE envolvente completa, dudoso frente a SATE fachada; incluye tramitación de CAEs sin descuento explícito; trae estimaciones de obra (SATE 102.910 IVA incl.; ascensor PEM 210.000)</t>
         </is>
       </c>
-      <c r="U88" s="2" t="n"/>
-      <c r="V88" s="2" t="inlineStr">
+      <c r="S88" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W88" s="2" t="inlineStr"/>
-      <c r="X88" s="4" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -8984,7 +8176,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>la misma enviada sirve a 2 firmadas; 2 hojas de Monday en esa dirección</t>
+          <t>la misma enviada sirve a 2 firmadas</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -9036,47 +8228,37 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · enviada_comunidad · 2026-01-30 · id 769afb42
-SATE + ASC · PROYECTO, SUBVENCION, CSS, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 9399686a</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>2</v>
+          <t>AV MARQUES DE CORBERA 24B MADRID PRY ASC + SUBV 04-02-2026 (SIN EFECTO).pdf</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>MARQUES DE CORBERA 24B MADRID - 30/01/2026 - PRY ASC+SUBV</t>
+        </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>AV MARQUES DE CORBERA 24B MADRID PRY ASC + SUBV 04-02-2026 (SIN EFECTO).pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>MARQUES DE CORBERA 24B MADRID - 30/01/2026 - PRY ASC+SUBV</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="S89" s="2" t="inlineStr"/>
-      <c r="T89" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 5.950 conjunto sin desglose; IEE/CEE solo si no hay uno previo válido; total_base = 6.940 + 1.980</t>
         </is>
       </c>
-      <c r="U89" s="2" t="n"/>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="S89" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr"/>
-      <c r="X89" s="4" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -9084,16 +8266,12 @@
           <t>088</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>2 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr">
         <is>
           <t>2026-02-04</t>
@@ -9143,47 +8321,37 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION, CEE, CSS, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 93cbf4e3
-INSTALACION DE ASCENSOR · enviada_comunidad · 2025-10-24 · id b95b161a</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>2</v>
+          <t>MARQUES DE CORBERA 22C MADRID ASC 04-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>MARQUES DE CORBERA 22C MADRID - 24/10/2025 - PRY ASC+SUBV</t>
+        </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>MARQUES DE CORBERA 22C MADRID ASC 04-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>MARQUES DE CORBERA 22C MADRID - 24/10/2025 - PRY ASC+SUBV</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="S90" s="2" t="inlineStr"/>
-      <c r="T90" s="2" t="inlineStr">
-        <is>
           <t>Total 5.900 son honorarios de proyecto; la subvención va aparte (1.980 fijo + 3,5% a éxito), no sumada en el total</t>
         </is>
       </c>
-      <c r="U90" s="2" t="n"/>
-      <c r="V90" s="2" t="inlineStr">
+      <c r="S90" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W90" s="2" t="inlineStr"/>
-      <c r="X90" s="4" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9247,46 +8415,37 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA · devuelta_firmada · 2026-01-22 · id c8737f55</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>1</v>
+          <t>ALFREDO ALEIX 20 MADRID SATE 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>ALFREDO ALEIX 20 MADRID - 22/01/2026 - SATECAES</t>
+        </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ALFREDO ALEIX 20 MADRID SATE 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>ALFREDO ALEIX 20 MADRID - 22/01/2026 - SATECAES</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="S91" s="2" t="inlineStr"/>
-      <c r="T91" s="2" t="inlineStr">
-        <is>
           <t>Importes por concepto son SIN descuento (suman 24.630); descuento CAES -16.130 deja total 8.500. Encaja con bloque SATE CON CESION DE CAES. IEE/CEE/LEE 'solo si es necesario' en el texto pero con precio en el desglose. PEM estimado 190.000. Conforme ya relleno (CP, CIF H79563490, cuenta). 'Envolvente térmica' casado como SATE envolvente completa.</t>
         </is>
       </c>
-      <c r="U91" s="2" t="n"/>
-      <c r="V91" s="2" t="inlineStr">
+      <c r="S91" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W91" s="2" t="inlineStr"/>
-      <c r="X91" s="4" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9294,16 +8453,12 @@
           <t>090</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t>2026-02-09</t>
@@ -9343,44 +8498,39 @@
           <t>A la contratación: 100% del total de los honorarios</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="n">
-        <v>0</v>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>AV EUROPA 20 ALCOBENDAS INF SUST ASC 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>AV EUROPA 20 ALCOBENDAS - 06/02/2026 - INFORME</t>
+        </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>AV EUROPA 20 ALCOBENDAS INF SUST ASC 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>AV EUROPA 20 ALCOBENDAS - 06/02/2026 - INFORME</t>
-        </is>
-      </c>
-      <c r="Q92" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr">
-        <is>
           <t>Informe para sustitución de ascensores; si hiciera falta proyecto/licencia los honorarios variarían</t>
         </is>
       </c>
-      <c r="U92" s="2" t="n"/>
-      <c r="V92" s="2" t="inlineStr">
+      <c r="S92" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W92" s="2" t="inlineStr"/>
-      <c r="X92" s="4" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -9449,46 +8599,37 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA · devuelta_firmada · 2025-12-16 · id e86c516f</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>1</v>
+          <t>FARO 4-6 MADRID SATE 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>FARO 4-6 MADRID  - 16/12/2025 - ENVOL</t>
+        </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>FARO 4-6 MADRID SATE 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>FARO 4-6 MADRID  - 16/12/2025 - ENVOL</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="S93" s="2" t="inlineStr"/>
-      <c r="T93" s="2" t="inlineStr">
-        <is>
           <t>'Envolvente térmica' asimilada a SATE envolvente completa; 'Gestion de CAES' sin bloque propio (SIN CASAR); IEE/CEE solo si no hay previos válidos; precio conjunto 17.000</t>
         </is>
       </c>
-      <c r="U93" s="2" t="n"/>
-      <c r="V93" s="2" t="inlineStr">
+      <c r="S93" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W93" s="2" t="inlineStr"/>
-      <c r="X93" s="4" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -9548,42 +8689,33 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCIÓN DE ASCENSORES · devuelta_firmada · 2026-02-06 · id 1afeef0f</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>1</v>
+          <t>LONDRES 13 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>LONDRES 13 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>LONDRES 13 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>LONDRES 13 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R94" s="2" t="inlineStr">
-        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="S94" s="2" t="inlineStr"/>
-      <c r="T94" s="2" t="n"/>
-      <c r="U94" s="2" t="n"/>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="n"/>
+      <c r="S94" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr"/>
-      <c r="X94" s="4" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9643,46 +8775,37 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCIÓN DE ASCENSORES · devuelta_firmada · 2026-02-06 · id 2562fa53</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>1</v>
+          <t>LONDRES 15 TORREJON DE ARDOZ 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>LONDRES 15 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>LONDRES 15 TORREJON DE ARDOZ 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>LONDRES 15 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="S95" s="2" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr">
-        <is>
           <t>Sustitución de ascensores casado como Modificación asc. Precio conjunto 2.800; no se reparte.</t>
         </is>
       </c>
-      <c r="U95" s="2" t="n"/>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="S95" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr"/>
-      <c r="X95" s="4" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9742,42 +8865,33 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCIÓN DE ASCENSORES · devuelta_firmada · 2026-02-06 · id b2547217</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>1</v>
+          <t>MILAN 1 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>MILAN 1 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>MILAN 1 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>MILAN 1 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R96" s="2" t="inlineStr">
-        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="n"/>
-      <c r="U96" s="2" t="n"/>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="n"/>
+      <c r="S96" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr"/>
-      <c r="X96" s="4" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9837,42 +8951,33 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCIÓN DE ASCENSORES · devuelta_firmada · 2026-02-06 · id 6c28bd77</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>1</v>
+          <t>MILAN 3 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>MILAN 3 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>MILAN 3 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>MILAN 3 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R97" s="2" t="inlineStr">
-        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr"/>
-      <c r="T97" s="2" t="n"/>
-      <c r="U97" s="2" t="n"/>
-      <c r="V97" s="2" t="inlineStr">
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="n"/>
+      <c r="S97" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W97" s="2" t="inlineStr"/>
-      <c r="X97" s="4" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9932,42 +9037,33 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCIÓN DE ASCENSORES · devuelta_firmada · 2026-02-06 · id e34feb15</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>1</v>
+          <t>MILAN 7 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>MILAN 7 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>MILAN 7 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>MILAN 7 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="inlineStr">
-        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="n"/>
-      <c r="U98" s="2" t="n"/>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="n"/>
+      <c r="S98" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr"/>
-      <c r="X98" s="4" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -10027,46 +9123,37 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>SUSTITUCIÓN DE ASCENSORES · devuelta_firmada · 2026-02-06 · id 6fddb1b2</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>1</v>
+          <t>MILAN 9 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>MILAN 9 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
+        </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>MILAN 9 TORREJON DE ARDOZ ASC 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>MILAN 9 TORREJON DE ARDOZ - 06/02/2026 - PRY SUST ASC</t>
-        </is>
-      </c>
-      <c r="Q99" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="S99" s="2" t="inlineStr"/>
-      <c r="T99" s="2" t="inlineStr">
-        <is>
           <t>Sustitución de ascensores casado como Modificación asc. Precio conjunto 2.800; no se reparte.</t>
         </is>
       </c>
-      <c r="U99" s="2" t="n"/>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="S99" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr"/>
-      <c r="X99" s="4" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -10136,46 +9223,37 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA  · devuelta_firmada · 2025-09-17 · id dc8b6e1f</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>1</v>
+          <t>SAN CLAUDIO 117 MADRID SATE 09-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>SAN CLAUDIO 117 MADRID - 17/09/2025 - SATE + SUBV CON CAES</t>
+        </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>SAN CLAUDIO 117 MADRID SATE 09-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>SAN CLAUDIO 117 MADRID - 17/09/2025 - SATE + SUBV CON CAES</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr">
-        <is>
           <t>Total sin descuento 26.070 (cuadra); descuento por cesión de CAES -17.570 deja 8.500 (posible bloque SATE CON CESION DE CAES); 'envolvente térmica' asimilada a SATE envolvente completa; CEE listado sin precio</t>
         </is>
       </c>
-      <c r="U100" s="2" t="n"/>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="S100" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr"/>
-      <c r="X100" s="4" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -10234,42 +9312,33 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>BAJADA A COTA 0 · devuelta_firmada · 2026-02-06 · id e3726a28</t>
-        </is>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>1</v>
+          <t>MIESES 2 LAS ROZAS - BAJADA A COTA 0 -10-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>MIESES 2 LAS ROZAS - 06/02/2026 - PRY BAJADA COTA 0</t>
+        </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>MIESES 2 LAS ROZAS - BAJADA A COTA 0 -10-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>MIESES 2 LAS ROZAS - 06/02/2026 - PRY BAJADA COTA 0</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R101" s="2" t="inlineStr">
-        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="n"/>
-      <c r="U101" s="2" t="n"/>
-      <c r="V101" s="2" t="inlineStr">
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="n"/>
+      <c r="S101" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr"/>
-      <c r="X101" s="4" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -10324,42 +9393,33 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>LEX · devuelta_firmada · 2025-11-12 · id 555b99cf</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>1</v>
+          <t>POLVORANCA 18 LEGANES LEE 11-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>POLVORANCA 18 LEGANES - 12/11/2025 - LEX</t>
+        </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>POLVORANCA 18 LEGANES LEE 11-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>POLVORANCA 18 LEGANES - 12/11/2025 - LEX</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R102" s="2" t="inlineStr">
-        <is>
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="n"/>
-      <c r="U102" s="2" t="n"/>
-      <c r="V102" s="2" t="inlineStr">
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="n"/>
+      <c r="S102" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W102" s="2" t="inlineStr"/>
-      <c r="X102" s="4" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -10418,46 +9478,37 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>OTRO · PROYECTO · devuelta_firmada · 2000-01-01 · id 569bf678</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>1</v>
+          <t>PEDRO UNANUE 22 MADRID - INFORME 17-02-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>PEDRO UNANUE 22 MADRID - 16/02/2026 - INFORME</t>
+        </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>PEDRO UNANUE 22 MADRID - INFORME 17-02-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>PEDRO UNANUE 22 MADRID - 16/02/2026 - INFORME</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="S103" s="2" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr">
-        <is>
           <t>La hoja dice 'UNANUME', el título del fichero 'UNANUE': posible errata en la calle.</t>
         </is>
       </c>
-      <c r="U103" s="2" t="n"/>
-      <c r="V103" s="2" t="inlineStr">
+      <c r="S103" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W103" s="2" t="inlineStr"/>
-      <c r="X103" s="4" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -10522,46 +9573,37 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA  · devuelta_firmada · 2026-01-15 · id a9dffbbd</t>
-        </is>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>1</v>
+          <t>MARIA PEDRAZA 25 MADRID SATE 06-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>MARIA PEDRAZA 25 MADRID - 15/01/2026 - PRY SATE +SUBV</t>
+        </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>MARIA PEDRAZA 25 MADRID SATE 06-03-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>MARIA PEDRAZA 25 MADRID - 15/01/2026 - PRY SATE +SUBV</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr">
-        <is>
           <t>'Envolvente térmica' asimilada a SATE envolvente completa; precio conjunto 8.500; IEE/CEE/LEE solo si son necesarios</t>
         </is>
       </c>
-      <c r="U104" s="2" t="n"/>
-      <c r="V104" s="2" t="inlineStr">
+      <c r="S104" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr"/>
-      <c r="X104" s="4" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -10569,16 +9611,12 @@
           <t>103</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>2 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr">
         <is>
           <t>2026-03-16</t>
@@ -10622,47 +9660,37 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION, CSS · devuelta_firmada · 2000-01-01 · id 2fdcc592
-TRAMITACION DE SUBVENCIONES · enviada_comunidad · 2026-03-04 · id 7e1b2d06</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>2</v>
+          <t>PLAZA VALSAIN 3 Y 4 MADRID - SUBV 16-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>PLAZA VALSAIN 3 Y 4  MADRID - 04/03/2026 - SUBV PRY PROP</t>
+        </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>PLAZA VALSAIN 3 Y 4 MADRID - SUBV 16-03-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>PLAZA VALSAIN 3 Y 4  MADRID - 04/03/2026 - SUBV PRY PROP</t>
-        </is>
-      </c>
-      <c r="Q105" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
-      <c r="T105" s="2" t="inlineStr">
-        <is>
           <t>Dos portales (3 y 4) en una sola hoja; IEE/CEE listados sin precio, solo si no hay previos válidos</t>
         </is>
       </c>
-      <c r="U105" s="2" t="n"/>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="S105" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr"/>
-      <c r="X105" s="4" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -10730,50 +9758,41 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA · devuelta_firmada · 2026-02-25 · id 24198a10</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>1</v>
+          <t>ISAAC PERAL 5 MOSTOLES SATE + CUBIERTA 17-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>ISAAC PERAL 5 MOSTOLES - 25/02/2026 - PRY SATE+SUBV</t>
+        </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ISAAC PERAL 5 MOSTOLES SATE + CUBIERTA 17-03-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>ISAAC PERAL 5 MOSTOLES - 25/02/2026 - PRY SATE+SUBV</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
+          <t>Modificado ISAAC PERAL 5 MOSTOLES - 25 02 2026 - PRY SATE+SUBV.gdoc</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>Proyecto 10.000 con descuento por cesión de CAES; subvención solo tramo variable 3,5%; incluye estudio SATE con coste de obra aprox. 204.692 IVA incl.; el objeto menciona también renovación de cubierta</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>Modificado ISAAC PERAL 5 MOSTOLES - 25 02 2026 - PRY SATE+SUBV.gdoc</t>
-        </is>
-      </c>
-      <c r="T106" s="2" t="inlineStr">
-        <is>
-          <t>Proyecto 10.000 con descuento por cesión de CAES; subvención solo tramo variable 3,5%; incluye estudio SATE con coste de obra aprox. 204.692 IVA incl.; el objeto menciona también renovación de cubierta</t>
-        </is>
-      </c>
-      <c r="U106" s="2" t="n"/>
-      <c r="V106" s="2" t="inlineStr">
-        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W106" s="2" t="inlineStr"/>
-      <c r="X106" s="4" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -10841,50 +9860,41 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA · devuelta_firmada · 2026-02-25 · id f6fc46f7</t>
-        </is>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>1</v>
+          <t>SIMON HERNANDEZ 43-45 MOSTOLES SATE + CUB 17-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>SIMON HERNANDEZ 43-45 MOSTOLES - 25/02/2026 - PRY SATE+SUBV</t>
+        </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>SIMON HERNANDEZ 43-45 MOSTOLES SATE + CUB 17-03-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>SIMON HERNANDEZ 43-45 MOSTOLES - 25/02/2026 - PRY SATE+SUBV</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
+          <t>Modificada -SIMON HERNANDEZ 43-45 MOSTOLES - 11 03 2026 - PRY SATE+SUBV.gdoc</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>Proyecto 24.400 precio conjunto; no se reparte. Habla de oferta con descuento por CAES pero no da importe del descuento. Dos números (43-45): ¿dos portales? Menciona también renovación de cubierta. Coste de obra aprox. 810.657.</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>Modificada -SIMON HERNANDEZ 43-45 MOSTOLES - 11 03 2026 - PRY SATE+SUBV.gdoc</t>
-        </is>
-      </c>
-      <c r="T107" s="2" t="inlineStr">
-        <is>
-          <t>Proyecto 24.400 precio conjunto; no se reparte. Habla de oferta con descuento por CAES pero no da importe del descuento. Dos números (43-45): ¿dos portales? Menciona también renovación de cubierta. Coste de obra aprox. 810.657.</t>
-        </is>
-      </c>
-      <c r="U107" s="2" t="n"/>
-      <c r="V107" s="2" t="inlineStr">
-        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr"/>
-      <c r="X107" s="4" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -10892,16 +9902,12 @@
           <t>106</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>2 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr">
         <is>
           <t>2026-03-19</t>
@@ -10951,47 +9957,37 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR · PROYECTO, SUBVENCION, CEE, CSS, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 82c08b5a
-INSTALACIÓN DE ASCENSOR · enviada_comunidad · 2026-01-30 · id bd2d58d8</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>2</v>
+          <t>AV MARQUES DE CORBERA 28B ASC 19-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>MARQUES DE CORBERA 28B MADRID - 30/01/2026 - PRY ASC+SUBV</t>
+        </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>AV MARQUES DE CORBERA 28B ASC 19-03-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>MARQUES DE CORBERA 28B MADRID - 30/01/2026 - PRY ASC+SUBV</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="S108" s="2" t="inlineStr"/>
-      <c r="T108" s="2" t="inlineStr">
-        <is>
           <t>Total 6.940 = Proyecto 5.950 + CSS 990; subvención aparte (1.980 fijo + 3,5% a éxito); su forma de pago dice 100% a la contratación sin mencionar el tramo variable</t>
         </is>
       </c>
-      <c r="U108" s="2" t="n"/>
-      <c r="V108" s="2" t="inlineStr">
+      <c r="S108" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W108" s="2" t="inlineStr"/>
-      <c r="X108" s="4" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -11053,46 +10049,37 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2026-01-23 · id b5f989b6</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>1</v>
+          <t>CAMARENA 304 MADRID ASC + SUBV 06-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>CAMARENA 304 MADRID - 23/01/2026 - ASCSUB</t>
+        </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>CAMARENA 304 MADRID ASC + SUBV 06-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>CAMARENA 304 MADRID - 23/01/2026 - ASCSUB</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="S109" s="2" t="inlineStr"/>
-      <c r="T109" s="2" t="inlineStr">
-        <is>
           <t>Total 6.900 son honorarios de proyecto; la subvención va aparte (1.980 fijo + 3,5% a éxito)</t>
         </is>
       </c>
-      <c r="U109" s="2" t="n"/>
-      <c r="V109" s="2" t="inlineStr">
+      <c r="S109" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W109" s="2" t="inlineStr"/>
-      <c r="X109" s="4" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -11100,16 +10087,12 @@
           <t>108</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
           <t>2026-04-07</t>
@@ -11154,48 +10137,39 @@
           <t>A la contratación (provisión de fondos) 50%; a la entrega del Proyecto 50% restante</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="n">
-        <v>0</v>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>ZARAGOZA 7 FUENLABRADA MEMORIA - 07-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>ZARAGOZA 7 FUENLABRADA - 25/03/2026 - PRY MEMORIA VALORADA</t>
+        </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ZARAGOZA 7 FUENLABRADA MEMORIA - 07-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>ZARAGOZA 7 FUENLABRADA - 25/03/2026 - PRY MEMORIA VALORADA</t>
-        </is>
-      </c>
-      <c r="Q110" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="S110" s="2" t="inlineStr"/>
-      <c r="T110" s="2" t="inlineStr">
-        <is>
           <t>Memoria valorada para mejora de accesibilidad pero con desglose de plantilla de proyecto; 'Proyecto 3500 + 735 IVA' incluye licencia, DF y CSS; código 2026/03/012</t>
         </is>
       </c>
-      <c r="U110" s="2" t="inlineStr">
-        <is>
-          <t>2026/03/012</t>
-        </is>
-      </c>
-      <c r="V110" s="2" t="inlineStr">
+      <c r="S110" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W110" s="2" t="inlineStr"/>
-      <c r="X110" s="4" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -11262,46 +10236,37 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2025-09-26 · id 82aff32e</t>
-        </is>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>1</v>
+          <t>VALMOJADO 243 MADRID ASC 08-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>VALMOJADO 243 MADRID - 01/10/2025 - PRY + SUBV</t>
+        </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>VALMOJADO 243 MADRID ASC 08-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>VALMOJADO 243 MADRID - 01/10/2025 - PRY + SUBV</t>
-        </is>
-      </c>
-      <c r="Q111" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr"/>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="S111" s="2" t="inlineStr"/>
-      <c r="T111" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 6.500 precio conjunto (pago 4.900 + 1.600 DF); IEE y CEE sin precio propio. Subvención limitada a una presentación por entidad (CAM y Ayto).</t>
         </is>
       </c>
-      <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="inlineStr">
+      <c r="S111" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W111" s="2" t="inlineStr"/>
-      <c r="X111" s="4" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -11361,42 +10326,33 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN ASCENSOR · devuelta_firmada · 2026-03-24 · id 79262d1a</t>
-        </is>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>1</v>
+          <t>RIO GENIL 10 MOSTOLES ASC - 10-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>RIO GENIL 10 MOSTOLES - 24/03/2026 - ASC</t>
+        </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>RIO GENIL 10 MOSTOLES ASC - 10-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>RIO GENIL 10 MOSTOLES - 24/03/2026 - ASC</t>
-        </is>
-      </c>
-      <c r="Q112" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R112" s="2" t="inlineStr">
-        <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="S112" s="2" t="inlineStr"/>
-      <c r="T112" s="2" t="n"/>
-      <c r="U112" s="2" t="n"/>
-      <c r="V112" s="2" t="inlineStr">
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="n"/>
+      <c r="S112" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W112" s="2" t="inlineStr"/>
-      <c r="X112" s="4" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -11456,50 +10412,37 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN ASCENSOR · devuelta_firmada · 2026-04-08 · id af4cbef8</t>
-        </is>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>1</v>
+          <t>EL PROVENCIO 31 MADRID ASC - 14-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>EL PROVENCIO 31 MADRID - 08/04/2026 - PRY ASC</t>
+        </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>EL PROVENCIO 31 MADRID ASC - 14-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>EL PROVENCIO 31 MADRID - 08/04/2026 - PRY ASC</t>
-        </is>
-      </c>
-      <c r="Q113" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr"/>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="S113" s="2" t="inlineStr"/>
-      <c r="T113" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 5.300 + 1.113 IVA = 6.413 incluye mediciones, licencia, DF y CSS; código 2026/04/004</t>
         </is>
       </c>
-      <c r="U113" s="2" t="inlineStr">
-        <is>
-          <t>2026/04/004</t>
-        </is>
-      </c>
-      <c r="V113" s="2" t="inlineStr">
+      <c r="S113" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W113" s="2" t="inlineStr"/>
-      <c r="X113" s="4" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -11507,16 +10450,12 @@
           <t>112</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
           <t>2026-04-14</t>
@@ -11561,40 +10500,35 @@
           <t>A la contratación (provisión de fondos) 50%; a la entrega del Proyecto 50% restante</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="n">
-        <v>0</v>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>KERRIA 30 ALCOBENDAS - ASC - 14-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>KERRIA 30 ALCOBENDAS - 22/12/2025 - PRY MODF 2 ASC</t>
+        </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>KERRIA 30 ALCOBENDAS - ASC - 14-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>KERRIA 30 ALCOBENDAS - 22/12/2025 - PRY MODF 2 ASC</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R114" s="2" t="inlineStr">
-        <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr"/>
-      <c r="T114" s="2" t="n"/>
-      <c r="U114" s="2" t="n"/>
-      <c r="V114" s="2" t="inlineStr">
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="n"/>
+      <c r="S114" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W114" s="2" t="inlineStr"/>
-      <c r="X114" s="4" t="inlineStr"/>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -11654,46 +10588,37 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2026-03-12 · id ba49c475</t>
-        </is>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>1</v>
+          <t>OLESA DE MONTSERRAT 34 MADRID - ASC - 14-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>OLESA DE MONTSERRAT 34 MADRID - 12/03/2026 - INSASC</t>
+        </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>OLESA DE MONTSERRAT 34 MADRID - ASC - 14-04-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>OLESA DE MONTSERRAT 34 MADRID - 12/03/2026 - INSASC</t>
-        </is>
-      </c>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr"/>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="S115" s="2" t="inlineStr"/>
-      <c r="T115" s="2" t="inlineStr">
-        <is>
           <t>Precio conjunto 6.720; no se reparte.</t>
         </is>
       </c>
-      <c r="U115" s="2" t="n"/>
-      <c r="V115" s="2" t="inlineStr">
+      <c r="S115" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W115" s="2" t="inlineStr"/>
-      <c r="X115" s="4" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -11753,46 +10678,37 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · devuelta_firmada · 2026-02-09 · id a0fc1f48</t>
-        </is>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>1</v>
+          <t>REAL VIEJA 5 SSRR - DF + SUBV (EXT)- 08-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>REAL VIEJA 5 SAN SEBASTIAN DE LOS REYES - 09/02/2026 - ASC</t>
+        </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>REAL VIEJA 5 SSRR - DF + SUBV (EXT)- 08-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>REAL VIEJA 5 SAN SEBASTIAN DE LOS REYES - 09/02/2026 - ASC</t>
-        </is>
-      </c>
-      <c r="Q116" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr"/>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="S116" s="2" t="inlineStr"/>
-      <c r="T116" s="2" t="inlineStr">
-        <is>
           <t>Proyecto externo: Accesalia hace DF de instalación de ascensor; honorarios de trabajos 5.000, subvención aparte (1.980 fijo + 3,5% a éxito)</t>
         </is>
       </c>
-      <c r="U116" s="2" t="n"/>
-      <c r="V116" s="2" t="inlineStr">
+      <c r="S116" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W116" s="2" t="inlineStr"/>
-      <c r="X116" s="4" t="inlineStr"/>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -11847,42 +10763,33 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>IEE · devuelta_firmada · 2026-03-04 · id 6aaadf9f</t>
-        </is>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>1</v>
+          <t>CASIMIRO ESCUDERO 11 MADRID IEE 11-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>CASIMIRO ESCUDERO 11 MADRID - 25/02/2026 - IEE</t>
+        </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>CASIMIRO ESCUDERO 11 MADRID IEE 11-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>CASIMIRO ESCUDERO 11 MADRID - 25/02/2026 - IEE</t>
-        </is>
-      </c>
-      <c r="Q117" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
-      <c r="R117" s="2" t="inlineStr">
-        <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S117" s="2" t="inlineStr"/>
-      <c r="T117" s="2" t="n"/>
-      <c r="U117" s="2" t="n"/>
-      <c r="V117" s="2" t="inlineStr">
+      <c r="Q117" s="2" t="inlineStr"/>
+      <c r="R117" s="2" t="n"/>
+      <c r="S117" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W117" s="2" t="inlineStr"/>
-      <c r="X117" s="4" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -11947,46 +10854,37 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE CUBIERTA · enviada_comunidad · 2026-02-25 · id 6e369070</t>
-        </is>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>1</v>
+          <t>EMPECINADO 23 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>EMPECINADO 23 MOSTOLES - 25/02/2026 - PRY REP CUBIERTA+SUBV</t>
+        </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>EMPECINADO 23 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>EMPECINADO 23 MOSTOLES - 25/02/2026 - PRY REP CUBIERTA+SUBV</t>
-        </is>
-      </c>
-      <c r="Q118" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr"/>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="S118" s="2" t="inlineStr"/>
-      <c r="T118" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.795 precio conjunto; subvención solo tramo variable 3,5%; coste de obra aprox. 71.000 + IVA idéntico en las hojas de Empecinado 23 y Salamanca 3, 5 y 7 (Móstoles)</t>
         </is>
       </c>
-      <c r="U118" s="2" t="n"/>
-      <c r="V118" s="2" t="inlineStr">
+      <c r="S118" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W118" s="2" t="inlineStr"/>
-      <c r="X118" s="4" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -12051,46 +10949,37 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE CUBIERTA · devuelta_firmada · 2026-02-25 · id 7cd385cf</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>1</v>
+          <t>SALAMANCA 1 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>SALAMANCA 1 MOSTOLES - 25/02/2026 - PRY REP CUBIERTA+SUBV</t>
+        </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 1 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 1 MOSTOLES - 25/02/2026 - PRY REP CUBIERTA+SUBV</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="S119" s="2" t="inlineStr"/>
-      <c r="T119" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.795 precio conjunto; no se reparte. Reparación de cubierta con subvención de eficiencia energética. Coste de obra aprox. 71.000.</t>
         </is>
       </c>
-      <c r="U119" s="2" t="n"/>
-      <c r="V119" s="2" t="inlineStr">
+      <c r="S119" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W119" s="2" t="inlineStr"/>
-      <c r="X119" s="4" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -12155,46 +11044,37 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE CUBIERTA · enviada_comunidad · 2026-02-25 · id 96cdfc4f</t>
-        </is>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>1</v>
+          <t>SALAMANCA 3 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>SALAMANCA 3 MOSTOLES - 25/02/2026 - PRY CUBIERTA+SUBV</t>
+        </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 3 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 3 MOSTOLES - 25/02/2026 - PRY CUBIERTA+SUBV</t>
-        </is>
-      </c>
-      <c r="Q120" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="S120" s="2" t="inlineStr"/>
-      <c r="T120" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.795 precio conjunto; subvención solo tramo variable 3,5%; coste de obra aprox. 71.000 + IVA idéntico en las hojas de Empecinado 23 y Salamanca 3, 5 y 7 (Móstoles)</t>
         </is>
       </c>
-      <c r="U120" s="2" t="n"/>
-      <c r="V120" s="2" t="inlineStr">
+      <c r="S120" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W120" s="2" t="inlineStr"/>
-      <c r="X120" s="4" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -12259,46 +11139,37 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE CUBIERTA · enviada_comunidad · 2026-02-25 · id b7047708</t>
-        </is>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>1</v>
+          <t>SALAMANCA 5 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>SALAMANCA 5 MOSTOLES - 25/02/2026 - PRY CUBIERTA+SUBV</t>
+        </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 5 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 5 MOSTOLES - 25/02/2026 - PRY CUBIERTA+SUBV</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr"/>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="S121" s="2" t="inlineStr"/>
-      <c r="T121" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.795 precio conjunto; subvención solo tramo variable 3,5%; coste de obra aprox. 71.000 + IVA idéntico en las hojas de Empecinado 23 y Salamanca 3, 5 y 7 (Móstoles)</t>
         </is>
       </c>
-      <c r="U121" s="2" t="n"/>
-      <c r="V121" s="2" t="inlineStr">
+      <c r="S121" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W121" s="2" t="inlineStr"/>
-      <c r="X121" s="4" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -12363,46 +11234,37 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE CUBIERTA · enviada_comunidad · 2026-02-25 · id a3d80fe4</t>
-        </is>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>1</v>
+          <t>SALAMANCA 7 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>SALAMANCA 7 MOSTOLES - 25/02/2026 - PRY CUBIERTA+SUBV</t>
+        </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 7 MOSTOLES CUBIERTA 12-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>SALAMANCA 7 MOSTOLES - 25/02/2026 - PRY CUBIERTA+SUBV</t>
-        </is>
-      </c>
-      <c r="Q122" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr"/>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="S122" s="2" t="inlineStr"/>
-      <c r="T122" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 3.795 precio conjunto; subvención solo tramo variable 3,5%; coste de obra aprox. 71.000 + IVA idéntico en las hojas de Empecinado 23 y Salamanca 3, 5 y 7 (Móstoles)</t>
         </is>
       </c>
-      <c r="U122" s="2" t="n"/>
-      <c r="V122" s="2" t="inlineStr">
+      <c r="S122" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W122" s="2" t="inlineStr"/>
-      <c r="X122" s="4" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -12470,50 +11332,41 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>ENVOLVENTE TERMICA · devuelta_firmada · 2026-02-25 · id 44c2b040</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>1</v>
+          <t>CASTELLON 15 MOSTOLES SATE + SUBV 13-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>CASTELLON 15 MOSTOLES - 25/02/2026 - PRY SATE+SUBV</t>
+        </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>CASTELLON 15 MOSTOLES SATE + SUBV 13-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>CASTELLON 15 MOSTOLES - 25/02/2026 - PRY SATE+SUBV</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
+          <t>MODIFICADO CASTELLON 15 MOSTOLES - 25 02 2026 - PRY SATE+SUBV.gdoc</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>Proyecto 10.000 precio conjunto; no se reparte. Habla de oferta con descuento por CAES pero no da importe del descuento. Menciona también renovación de cubierta. Coste de obra aprox. 268.042 IVA incluido.</t>
         </is>
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>MODIFICADO CASTELLON 15 MOSTOLES - 25 02 2026 - PRY SATE+SUBV.gdoc</t>
-        </is>
-      </c>
-      <c r="T123" s="2" t="inlineStr">
-        <is>
-          <t>Proyecto 10.000 precio conjunto; no se reparte. Habla de oferta con descuento por CAES pero no da importe del descuento. Menciona también renovación de cubierta. Coste de obra aprox. 268.042 IVA incluido.</t>
-        </is>
-      </c>
-      <c r="U123" s="2" t="n"/>
-      <c r="V123" s="2" t="inlineStr">
-        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W123" s="2" t="inlineStr"/>
-      <c r="X123" s="4" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -12528,7 +11381,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>la misma enviada sirve a 2 firmadas; 2 hojas de Monday en esa dirección</t>
+          <t>la misma enviada sirve a 2 firmadas</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -12580,47 +11433,37 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE ASCENSOR · enviada_comunidad · 2026-01-30 · id 769afb42
-SATE + ASC · PROYECTO, SUBVENCION, CSS, DIR. OBRA · devuelta_firmada · 2000-01-01 · id 9399686a</t>
-        </is>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>2</v>
+          <t>AV MARQUES DE CORBERA 24B MADRID ASC + SATE + SUBV 14-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>MARQUES DE CORBERA 24B MADRID - 30/01/2026 - PRY ASC+SUBV</t>
+        </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>AV MARQUES DE CORBERA 24B MADRID ASC + SATE + SUBV 14-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>MARQUES DE CORBERA 24B MADRID - 30/01/2026 - PRY ASC+SUBV</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr"/>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="S124" s="2" t="inlineStr"/>
-      <c r="T124" s="2" t="inlineStr">
-        <is>
           <t>Total 6.940 = Proyecto 5.950 + CSS 990; subvención aparte (1.980 fijo + 3,5% a éxito); su forma de pago dice 100% a la contratación sin mencionar el tramo variable</t>
         </is>
       </c>
-      <c r="U124" s="2" t="n"/>
-      <c r="V124" s="2" t="inlineStr">
+      <c r="S124" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W124" s="2" t="inlineStr"/>
-      <c r="X124" s="4" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -12687,50 +11530,41 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>INSTALACION DE ASCENSOR  · devuelta_firmada · 2025-12-16 · id 74ab3a38</t>
-        </is>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>1</v>
+          <t>TUBO 5 HUMERA ASC (4) + ELEVADOR 29-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>TUBO 5 HUMERA - 11/05/20256- ASC SUB</t>
+        </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>TUBO 5 HUMERA ASC (4) + ELEVADOR 29-05-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>TUBO 5 HUMERA - 11/05/20256- ASC SUB</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
+          <t>modificado tras reunión TUBO 5 HUMERA - 28 05 20256- ASC SUB.gdoc</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>4 ascensores y 1 elevador exterior en una hoja; subvención aparte (2.500 fijo + 3,5% a éxito); plazo de proyecto máx. 4 meses; título con fecha mal escrita '11/05/20256'</t>
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>modificado tras reunión TUBO 5 HUMERA - 28 05 20256- ASC SUB.gdoc</t>
-        </is>
-      </c>
-      <c r="T125" s="2" t="inlineStr">
-        <is>
-          <t>4 ascensores y 1 elevador exterior en una hoja; subvención aparte (2.500 fijo + 3,5% a éxito); plazo de proyecto máx. 4 meses; título con fecha mal escrita '11/05/20256'</t>
-        </is>
-      </c>
-      <c r="U125" s="2" t="n"/>
-      <c r="V125" s="2" t="inlineStr">
-        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W125" s="2" t="inlineStr"/>
-      <c r="X125" s="4" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -12790,50 +11624,37 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN ASCENSOR · devuelta_firmada · 2026-06-01 · id 0cce6ce0</t>
-        </is>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>1</v>
+          <t>RIO GENIL 7 MOSTOLES - ASC - 01-06-2026 - .pdf</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>RIO GENIL 7 MOSTOLES - 01/06/2026 - PRY ASC +CSS</t>
+        </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>RIO GENIL 7 MOSTOLES - ASC - 01-06-2026 - .pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>RIO GENIL 7 MOSTOLES - 01/06/2026 - PRY ASC +CSS</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr"/>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="S126" s="2" t="inlineStr"/>
-      <c r="T126" s="2" t="inlineStr">
-        <is>
           <t>No hay total explícito: 5.800 = Proyecto 4.880 + CSS 920; código 2026/05/121</t>
         </is>
       </c>
-      <c r="U126" s="2" t="inlineStr">
-        <is>
-          <t>2026/05/121</t>
-        </is>
-      </c>
-      <c r="V126" s="2" t="inlineStr">
+      <c r="S126" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W126" s="2" t="inlineStr"/>
-      <c r="X126" s="4" t="inlineStr"/>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -12896,50 +11717,37 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCIONES · devuelta_firmada · 2026-04-20 · id 1e2ec6cf</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>1</v>
+          <t>BALAGUER 4 MADRID - SUBV EXT 03-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>BALAGUER 4 MADRID - 20/04/2026 - SUBVENCIONES ACCESIBILIDAD</t>
+        </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>BALAGUER 4 MADRID - SUBV EXT 03-06-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>BALAGUER 4 MADRID - 20/04/2026 - SUBVENCIONES ACCESIBILIDAD</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr"/>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
-      <c r="T127" s="2" t="inlineStr">
-        <is>
           <t>Documentación Técnica Anexa 1.980 SIN CASAR: incluye IEE + CEE + comparativa de 3 presupuestos. Lleva código 2026/04/013.</t>
         </is>
       </c>
-      <c r="U127" s="2" t="inlineStr">
-        <is>
-          <t>2026/04/013</t>
-        </is>
-      </c>
-      <c r="V127" s="2" t="inlineStr">
+      <c r="S127" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W127" s="2" t="inlineStr"/>
-      <c r="X127" s="4" t="inlineStr"/>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -13008,50 +11816,37 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>ASCENSOR + SUBVENCIONES · devuelta_firmada · 2026-05-05 · id 0043e053</t>
-        </is>
-      </c>
-      <c r="N128" s="2" t="n">
-        <v>1</v>
+          <t>ISTURIZ 9 MADRID - ASC + SUBV - 08-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>ISTURIZ 9 MADRID - 05/05/2026 - PRY ASC + SUBV</t>
+        </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>ISTURIZ 9 MADRID - ASC + SUBV - 08-06-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>ISTURIZ 9 MADRID - 05/05/2026 - PRY ASC + SUBV</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr"/>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="S128" s="2" t="inlineStr"/>
-      <c r="T128" s="2" t="inlineStr">
-        <is>
           <t>Sin total explícito: 8.880 = Proyecto 5.980 + CSS 920 + Documentación Técnica Anexa 1.980; la Doc. Técnica Anexa (IEE+CEE+comparativa 3 presupuestos) va SIN CASAR; código 2026/04/054</t>
         </is>
       </c>
-      <c r="U128" s="2" t="inlineStr">
-        <is>
-          <t>2026/04/054</t>
-        </is>
-      </c>
-      <c r="V128" s="2" t="inlineStr">
+      <c r="S128" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W128" s="2" t="inlineStr"/>
-      <c r="X128" s="4" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -13113,46 +11908,37 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>INSTALACION DE ASCENSOR  · devuelta_firmada · 2025-12-22 · id d9fdfa1a</t>
-        </is>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>1</v>
+          <t>PABLO LAFARGUE 38 MADRID - ASC+SUBV - 08-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>PABLO LAFARGUE 38 MADRID - 22/12/2025 - ASC</t>
+        </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>PABLO LAFARGUE 38 MADRID - ASC+SUBV - 08-06-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>PABLO LAFARGUE 38 MADRID - 22/12/2025 - ASC</t>
-        </is>
-      </c>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr"/>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="S129" s="2" t="inlineStr"/>
-      <c r="T129" s="2" t="inlineStr">
-        <is>
           <t>Total 6.900 son honorarios de proyecto; la subvención va aparte (1.980 fijo + 3,5% a éxito)</t>
         </is>
       </c>
-      <c r="U129" s="2" t="n"/>
-      <c r="V129" s="2" t="inlineStr">
+      <c r="S129" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W129" s="2" t="inlineStr"/>
-      <c r="X129" s="4" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -13215,42 +12001,33 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE SUBVENCIONES  · devuelta_firmada · 2026-03-19 · id ee3bb010</t>
-        </is>
-      </c>
-      <c r="N130" s="2" t="n">
-        <v>1</v>
+          <t>ACEUCHAL 18 MADRID - SUBV - 09-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>HOJA DE ENCARGO aceuchal 18 madrid PRY+CSS.pdf</t>
+        </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ACEUCHAL 18 MADRID - SUBV - 09-06-2026.pdf</t>
-        </is>
-      </c>
-      <c r="P130" s="2" t="inlineStr">
-        <is>
-          <t>HOJA DE ENCARGO aceuchal 18 madrid PRY+CSS.pdf</t>
-        </is>
-      </c>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
           <t>PRESUPUESTOS ENVIADOS</t>
         </is>
       </c>
-      <c r="R130" s="2" t="inlineStr"/>
-      <c r="S130" s="2" t="inlineStr"/>
-      <c r="T130" s="2" t="inlineStr">
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr"/>
+      <c r="R130" s="2" t="inlineStr">
         <is>
           <t>proyecto+licencia+DF+CFO a precio conjunto de 3.500; las fracciones de pago se perdieron en el texto (probablemente 1/3 cada una); en la casilla CIF pone la razón social</t>
         </is>
       </c>
-      <c r="U130" s="2" t="n"/>
-      <c r="V130" s="2" t="inlineStr">
+      <c r="S130" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W130" s="2" t="inlineStr"/>
-      <c r="X130" s="4" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -13313,50 +12090,37 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN SUBVENCIONES · devuelta_firmada · 2026-05-26 · id fff5a720</t>
-        </is>
-      </c>
-      <c r="N131" s="2" t="n">
-        <v>1</v>
+          <t>FRANCISCO FATOU 26 MADRID SUBV EXT 15-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO FATOU 26 MADRID - 26/05/2026 - SUBVENCIONES EXTERNO</t>
+        </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO FATOU 26 MADRID SUBV EXT 15-06-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO FATOU 26 MADRID - 26/05/2026 - SUBVENCIONES EXTERNO</t>
-        </is>
-      </c>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr"/>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="S131" s="2" t="inlineStr"/>
-      <c r="T131" s="2" t="inlineStr">
-        <is>
           <t>Proyecto externo (solo subvenciones); Documentación Técnica Anexa 2.225 (IEE+CEE+comparativa 3 presupuestos) va SIN CASAR; código 2026/05/102</t>
         </is>
       </c>
-      <c r="U131" s="2" t="inlineStr">
-        <is>
-          <t>2026/05/102</t>
-        </is>
-      </c>
-      <c r="V131" s="2" t="inlineStr">
+      <c r="S131" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W131" s="2" t="inlineStr"/>
-      <c r="X131" s="4" t="inlineStr"/>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -13415,50 +12179,37 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN ASCENSOR · devuelta_firmada · 2026-05-22 · id 7095b098</t>
-        </is>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>1</v>
+          <t>GALLEGOS 12 ALCALA DE HENARES (INTERIOR) - ASC - 18-06-2026 CONTRATO TKE.pdf</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>GALLEGOS 12 ALCALA DE HENARES - 22/05/2026 - INSTALACIÓN ASCENSOR</t>
+        </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>GALLEGOS 12 ALCALA DE HENARES (INTERIOR) - ASC - 18-06-2026 CONTRATO TKE.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>GALLEGOS 12 ALCALA DE HENARES - 22/05/2026 - INSTALACIÓN ASCENSOR</t>
-        </is>
-      </c>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr"/>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="S132" s="2" t="inlineStr"/>
-      <c r="T132" s="2" t="inlineStr">
-        <is>
           <t>Proyecto 5.000 incluye proyecto, licencia y DF; toma de datos y fin de obra salen en el desglose pero no en el 'Incluye'. Lleva código 2026/05/088.</t>
         </is>
       </c>
-      <c r="U132" s="2" t="inlineStr">
-        <is>
-          <t>2026/05/088</t>
-        </is>
-      </c>
-      <c r="V132" s="2" t="inlineStr">
+      <c r="S132" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W132" s="2" t="inlineStr"/>
-      <c r="X132" s="4" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -13514,46 +12265,37 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>IEE · devuelta_firmada · 2026-03-16 · id 85975450</t>
-        </is>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>1</v>
+          <t>CARLOS SOLE 44 MADRID - IEE - 02-07-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>CARLOS SOLE 44 MADRID - 16/03/2026 - IEE</t>
+        </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>CARLOS SOLE 44 MADRID - IEE - 02-07-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>CARLOS SOLE 44 MADRID - 16/03/2026 - IEE</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr"/>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="S133" s="2" t="inlineStr"/>
-      <c r="T133" s="2" t="inlineStr">
-        <is>
           <t>Importe dado como '1.190 € IVA INCLUIDO': base calculada 1.190/1,21 = 983,47; es IEE de garaje e incluye informe para recolocar rejillas de ventilación</t>
         </is>
       </c>
-      <c r="U133" s="2" t="n"/>
-      <c r="V133" s="2" t="inlineStr">
+      <c r="S133" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W133" s="2" t="inlineStr"/>
-      <c r="X133" s="4" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -13617,46 +12359,37 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN SUBVENCIONES · enviada_comunidad · 2026-07-17 · id f2fdbce5</t>
-        </is>
-      </c>
-      <c r="N134" s="2" t="n">
-        <v>1</v>
+          <t>NAVARRA 28-30 MADRID - SUBV EXT- 29-07-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>NAVARRA 28-30 MADRID - 17/07/2026 - SUBV PROY EXT</t>
+        </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>NAVARRA 28-30 MADRID - SUBV EXT- 29-07-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>NAVARRA 28-30 MADRID - 17/07/2026 - SUBV PROY EXT</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr"/>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="S134" s="2" t="inlineStr"/>
-      <c r="T134" s="2" t="inlineStr">
-        <is>
           <t>Proyecto externo (solo subvenciones); dos números (28-30) en una hoja; a éxito 4,5% (no el 3,5% habitual); Documentación Técnica Anexa 2.225 SIN CASAR (IEE+CEE+comparativa libres de costo); LEE listado sin precio, solo si la convocatoria lo exige</t>
         </is>
       </c>
-      <c r="U134" s="2" t="n"/>
-      <c r="V134" s="2" t="inlineStr">
+      <c r="S134" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W134" s="2" t="inlineStr"/>
-      <c r="X134" s="4" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -13671,7 +12404,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>0 hojas de Monday en esa dirección; concepto sin casar con el catálogo</t>
+          <t>concepto sin casar con el catálogo</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -13718,44 +12451,39 @@
           <t>A la contratación (provisión de fondos) 50%; a la entrega 50% restante</t>
         </is>
       </c>
-      <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="n">
-        <v>0</v>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>HONDURAS 20 COSLADA - INFORME - 30-07-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>HONDURAS 20 COSLADA - 28/07/2026 - INFORME</t>
+        </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>HONDURAS 20 COSLADA - INFORME - 30-07-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>HONDURAS 20 COSLADA - 28/07/2026 - INFORME</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr"/>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="S135" s="2" t="inlineStr"/>
-      <c r="T135" s="2" t="inlineStr">
-        <is>
           <t>Informe de instalación de 2 ascensores con asesoramiento sobre ayudas dentro del mismo precio (SIN CASAR); si hiciera falta proyecto/licencia los honorarios variarían</t>
         </is>
       </c>
-      <c r="U135" s="2" t="n"/>
-      <c r="V135" s="2" t="inlineStr">
+      <c r="S135" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W135" s="2" t="inlineStr"/>
-      <c r="X135" s="4" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -13763,16 +12491,12 @@
           <t>134</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>0 hojas de Monday en esa dirección</t>
-        </is>
-      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -13812,44 +12536,39 @@
           <t>A la contratación, en concepto de provisión de fondos: 50% del total de los honorarios. A la entrega: 50% restante.</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="2" t="n">
-        <v>0</v>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>PIZARRO 4 TORREJON DE ARDOZ - INFORME - 30-07-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>PIZARRO 4 TORREJON DE ARDOZ - 28/07/2026 - INFORME</t>
+        </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>PIZARRO 4 TORREJON DE ARDOZ - INFORME - 30-07-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>PIZARRO 4 TORREJON DE ARDOZ - 28/07/2026 - INFORME</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr"/>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="S136" s="2" t="inlineStr"/>
-      <c r="T136" s="2" t="inlineStr">
-        <is>
           <t>Informe para modificación de ascensor; si hiciera falta proyecto o licencia, los honorarios variarían.</t>
         </is>
       </c>
-      <c r="U136" s="2" t="n"/>
-      <c r="V136" s="2" t="inlineStr">
+      <c r="S136" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W136" s="2" t="inlineStr"/>
-      <c r="X136" s="4" t="inlineStr"/>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -13864,7 +12583,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>0 hojas de Monday en esa dirección; concepto sin casar con el catálogo</t>
+          <t>concepto sin casar con el catálogo</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -13908,47 +12627,42 @@
           <t>A la contratación (provisión de fondos) 50%; a la entrega del Proyecto 50% restante</t>
         </is>
       </c>
-      <c r="M137" s="2" t="inlineStr"/>
-      <c r="N137" s="2" t="n">
-        <v>0</v>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>FERENC PUSKAS 28 MADRID - MEDICIONES Y CIEGO - 25-09-2026.pdf</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>FERENC PUSKAS 28 MADRID - 11/09/2026 - MEDICIONES Y CIEGO</t>
+        </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>FERENC PUSKAS 28 MADRID - MEDICIONES Y CIEGO - 25-09-2026.pdf</t>
+          <t>HOJAS ENCARGO AUTOMATICAS</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>FERENC PUSKAS 28 MADRID - 11/09/2026 - MEDICIONES Y CIEGO</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>HOJAS ENCARGO AUTOMATICAS</t>
-        </is>
-      </c>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr"/>
       <c r="R137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S137" s="2" t="inlineStr"/>
-      <c r="T137" s="2" t="inlineStr">
-        <is>
           <t>Encargo de mediciones y presupuesto ciego (sin tipo en el catálogo); precio conjunto 1.650; la forma de pago habla de 'entrega del Proyecto' aunque no hay proyecto</t>
         </is>
       </c>
-      <c r="U137" s="2" t="n"/>
-      <c r="V137" s="2" t="inlineStr">
+      <c r="S137" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="W137" s="2" t="inlineStr"/>
-      <c r="X137" s="4" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X137"/>
+  <autoFilter ref="A1:U137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
